--- a/_docs/trim_02/Casos de Uso Documentados/_Especificación de casos de uso adso.xlsx
+++ b/_docs/trim_02/Casos de Uso Documentados/_Especificación de casos de uso adso.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ccifu\OneDrive\Escritorio\AXXION_SYSTEM\_docs\trim_02\Casos de Uso Documentados\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF08C854-C232-4DA0-8E4B-0D4D82549F2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6398194B-0A0A-4A85-91AA-B214E733A30E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="13" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="11" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Iniciar sesión" sheetId="1" r:id="rId1"/>
@@ -1097,47 +1097,62 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1151,6 +1166,33 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -1160,46 +1202,10 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1208,11 +1214,14 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1222,15 +1231,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1464,28 +1464,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="21" t="s">
+      <c r="B1" s="29"/>
+      <c r="C1" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="22"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="29"/>
     </row>
     <row r="2" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="22"/>
-      <c r="C2" s="31" t="s">
+      <c r="B2" s="29"/>
+      <c r="C2" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="30"/>
-      <c r="E2" s="22"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="29"/>
       <c r="F2" s="1" t="s">
         <v>4</v>
       </c>
@@ -1494,248 +1494,248 @@
       </c>
     </row>
     <row r="3" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A3" s="21" t="s">
+      <c r="A3" s="32" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="22"/>
-      <c r="C3" s="31" t="s">
+      <c r="B3" s="29"/>
+      <c r="C3" s="27" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="30"/>
-      <c r="E3" s="30"/>
-      <c r="F3" s="30"/>
-      <c r="G3" s="22"/>
+      <c r="D3" s="28"/>
+      <c r="E3" s="28"/>
+      <c r="F3" s="28"/>
+      <c r="G3" s="29"/>
     </row>
     <row r="4" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A4" s="21" t="s">
+      <c r="A4" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="22"/>
-      <c r="C4" s="32">
+      <c r="B4" s="29"/>
+      <c r="C4" s="42">
         <v>45786</v>
       </c>
-      <c r="D4" s="30"/>
-      <c r="E4" s="30"/>
-      <c r="F4" s="30"/>
-      <c r="G4" s="22"/>
+      <c r="D4" s="28"/>
+      <c r="E4" s="28"/>
+      <c r="F4" s="28"/>
+      <c r="G4" s="29"/>
     </row>
     <row r="5" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A5" s="21" t="s">
+      <c r="A5" s="32" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="22"/>
-      <c r="C5" s="31" t="s">
+      <c r="B5" s="29"/>
+      <c r="C5" s="27" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="30"/>
-      <c r="E5" s="30"/>
-      <c r="F5" s="30"/>
-      <c r="G5" s="22"/>
+      <c r="D5" s="28"/>
+      <c r="E5" s="28"/>
+      <c r="F5" s="28"/>
+      <c r="G5" s="29"/>
     </row>
     <row r="6" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A6" s="23" t="s">
+      <c r="A6" s="35" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="24"/>
+      <c r="B6" s="36"/>
       <c r="C6" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D6" s="31" t="s">
+      <c r="D6" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="E6" s="30"/>
-      <c r="F6" s="30"/>
-      <c r="G6" s="22"/>
+      <c r="E6" s="28"/>
+      <c r="F6" s="28"/>
+      <c r="G6" s="29"/>
     </row>
     <row r="7" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="25"/>
-      <c r="B7" s="26"/>
+      <c r="A7" s="39"/>
+      <c r="B7" s="40"/>
       <c r="C7" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D7" s="33"/>
-      <c r="E7" s="34"/>
-      <c r="F7" s="34"/>
-      <c r="G7" s="26"/>
+      <c r="D7" s="43"/>
+      <c r="E7" s="44"/>
+      <c r="F7" s="44"/>
+      <c r="G7" s="40"/>
     </row>
     <row r="8" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="27" t="s">
+      <c r="A8" s="41" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="22"/>
-      <c r="C8" s="35" t="s">
+      <c r="B8" s="29"/>
+      <c r="C8" s="31" t="s">
         <v>109</v>
       </c>
-      <c r="D8" s="30"/>
-      <c r="E8" s="30"/>
-      <c r="F8" s="30"/>
-      <c r="G8" s="22"/>
+      <c r="D8" s="28"/>
+      <c r="E8" s="28"/>
+      <c r="F8" s="28"/>
+      <c r="G8" s="29"/>
     </row>
     <row r="9" spans="1:7" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="27" t="s">
+      <c r="A9" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="22"/>
-      <c r="C9" s="35" t="s">
+      <c r="B9" s="29"/>
+      <c r="C9" s="31" t="s">
         <v>110</v>
       </c>
-      <c r="D9" s="30"/>
-      <c r="E9" s="30"/>
-      <c r="F9" s="30"/>
-      <c r="G9" s="22"/>
+      <c r="D9" s="28"/>
+      <c r="E9" s="28"/>
+      <c r="F9" s="28"/>
+      <c r="G9" s="29"/>
     </row>
     <row r="10" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A10" s="23" t="s">
+      <c r="A10" s="35" t="s">
         <v>16</v>
       </c>
-      <c r="B10" s="24"/>
+      <c r="B10" s="36"/>
       <c r="C10" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D10" s="48" t="s">
+      <c r="D10" s="33" t="s">
         <v>137</v>
       </c>
-      <c r="E10" s="49"/>
-      <c r="F10" s="48" t="s">
+      <c r="E10" s="34"/>
+      <c r="F10" s="33" t="s">
         <v>138</v>
       </c>
-      <c r="G10" s="49"/>
+      <c r="G10" s="34"/>
     </row>
     <row r="11" spans="1:7" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="28"/>
-      <c r="B11" s="29"/>
+      <c r="A11" s="37"/>
+      <c r="B11" s="38"/>
       <c r="C11" s="5">
         <v>1</v>
       </c>
-      <c r="D11" s="50" t="s">
+      <c r="D11" s="26" t="s">
         <v>139</v>
       </c>
-      <c r="E11" s="51"/>
-      <c r="F11" s="52" t="s">
+      <c r="E11" s="25"/>
+      <c r="F11" s="22" t="s">
         <v>140</v>
       </c>
-      <c r="G11" s="53"/>
+      <c r="G11" s="23"/>
     </row>
     <row r="12" spans="1:7" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="28"/>
-      <c r="B12" s="29"/>
+      <c r="A12" s="37"/>
+      <c r="B12" s="38"/>
       <c r="C12" s="5">
         <v>2</v>
       </c>
-      <c r="D12" s="54" t="s">
+      <c r="D12" s="24" t="s">
         <v>141</v>
       </c>
-      <c r="E12" s="51"/>
-      <c r="F12" s="52"/>
-      <c r="G12" s="53"/>
+      <c r="E12" s="25"/>
+      <c r="F12" s="22"/>
+      <c r="G12" s="23"/>
     </row>
     <row r="13" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A13" s="28"/>
-      <c r="B13" s="29"/>
+      <c r="A13" s="37"/>
+      <c r="B13" s="38"/>
       <c r="C13" s="5">
         <v>3</v>
       </c>
-      <c r="D13" s="54" t="s">
+      <c r="D13" s="24" t="s">
         <v>142</v>
       </c>
-      <c r="E13" s="51"/>
-      <c r="F13" s="52" t="s">
+      <c r="E13" s="25"/>
+      <c r="F13" s="22" t="s">
         <v>143</v>
       </c>
-      <c r="G13" s="53"/>
+      <c r="G13" s="23"/>
     </row>
     <row r="14" spans="1:7" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="28"/>
-      <c r="B14" s="29"/>
+      <c r="A14" s="37"/>
+      <c r="B14" s="38"/>
       <c r="C14" s="5">
         <v>4</v>
       </c>
-      <c r="D14" s="50"/>
-      <c r="E14" s="51"/>
-      <c r="F14" s="52" t="s">
+      <c r="D14" s="26"/>
+      <c r="E14" s="25"/>
+      <c r="F14" s="22" t="s">
         <v>144</v>
       </c>
-      <c r="G14" s="53"/>
+      <c r="G14" s="23"/>
     </row>
     <row r="15" spans="1:7" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="28"/>
-      <c r="B15" s="29"/>
+      <c r="A15" s="37"/>
+      <c r="B15" s="38"/>
       <c r="C15" s="5">
         <v>5</v>
       </c>
-      <c r="D15" s="50"/>
-      <c r="E15" s="51"/>
-      <c r="F15" s="52" t="s">
+      <c r="D15" s="26"/>
+      <c r="E15" s="25"/>
+      <c r="F15" s="22" t="s">
         <v>145</v>
       </c>
-      <c r="G15" s="53"/>
+      <c r="G15" s="23"/>
     </row>
     <row r="16" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="23" t="s">
+      <c r="A16" s="35" t="s">
         <v>19</v>
       </c>
-      <c r="B16" s="24"/>
+      <c r="B16" s="36"/>
       <c r="C16" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D16" s="21" t="s">
+      <c r="D16" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="E16" s="30"/>
-      <c r="F16" s="30"/>
-      <c r="G16" s="22"/>
+      <c r="E16" s="28"/>
+      <c r="F16" s="28"/>
+      <c r="G16" s="29"/>
     </row>
     <row r="17" spans="1:7" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="28"/>
-      <c r="B17" s="29"/>
+      <c r="A17" s="37"/>
+      <c r="B17" s="38"/>
       <c r="C17" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="D17" s="36" t="s">
+      <c r="D17" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="E17" s="30"/>
-      <c r="F17" s="30"/>
-      <c r="G17" s="22"/>
+      <c r="E17" s="28"/>
+      <c r="F17" s="28"/>
+      <c r="G17" s="29"/>
     </row>
     <row r="18" spans="1:7" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="28"/>
-      <c r="B18" s="29"/>
+      <c r="A18" s="37"/>
+      <c r="B18" s="38"/>
       <c r="C18" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="D18" s="36" t="s">
+      <c r="D18" s="30" t="s">
         <v>23</v>
       </c>
-      <c r="E18" s="30"/>
-      <c r="F18" s="30"/>
-      <c r="G18" s="22"/>
+      <c r="E18" s="28"/>
+      <c r="F18" s="28"/>
+      <c r="G18" s="29"/>
     </row>
     <row r="19" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A19" s="25"/>
-      <c r="B19" s="26"/>
+      <c r="A19" s="39"/>
+      <c r="B19" s="40"/>
       <c r="C19" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="D19" s="36" t="s">
+      <c r="D19" s="30" t="s">
         <v>25</v>
       </c>
-      <c r="E19" s="30"/>
-      <c r="F19" s="30"/>
-      <c r="G19" s="22"/>
+      <c r="E19" s="28"/>
+      <c r="F19" s="28"/>
+      <c r="G19" s="29"/>
     </row>
     <row r="20" spans="1:7" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="27" t="s">
+      <c r="A20" s="41" t="s">
         <v>26</v>
       </c>
-      <c r="B20" s="22"/>
-      <c r="C20" s="35" t="s">
+      <c r="B20" s="29"/>
+      <c r="C20" s="31" t="s">
         <v>111</v>
       </c>
-      <c r="D20" s="30"/>
-      <c r="E20" s="30"/>
-      <c r="F20" s="30"/>
-      <c r="G20" s="22"/>
+      <c r="D20" s="28"/>
+      <c r="E20" s="28"/>
+      <c r="F20" s="28"/>
+      <c r="G20" s="29"/>
     </row>
     <row r="21" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="22" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -2433,24 +2433,9 @@
     <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="37">
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="D6:G6"/>
-    <mergeCell ref="D19:G19"/>
-    <mergeCell ref="C20:G20"/>
-    <mergeCell ref="D16:G16"/>
-    <mergeCell ref="D17:G17"/>
-    <mergeCell ref="D18:G18"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="A6:B7"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A9:B9"/>
     <mergeCell ref="A16:B19"/>
     <mergeCell ref="A20:B20"/>
     <mergeCell ref="A10:B15"/>
@@ -2467,9 +2452,24 @@
     <mergeCell ref="C9:G9"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A6:B7"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="D19:G19"/>
+    <mergeCell ref="C20:G20"/>
+    <mergeCell ref="D16:G16"/>
+    <mergeCell ref="D17:G17"/>
+    <mergeCell ref="D18:G18"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="D6:G6"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="F11:G11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2490,28 +2490,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="21" t="s">
+      <c r="B1" s="29"/>
+      <c r="C1" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="22"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="29"/>
     </row>
     <row r="2" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="22"/>
-      <c r="C2" s="38" t="s">
+      <c r="B2" s="29"/>
+      <c r="C2" s="56" t="s">
         <v>100</v>
       </c>
-      <c r="D2" s="30"/>
-      <c r="E2" s="22"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="29"/>
       <c r="F2" s="1" t="s">
         <v>4</v>
       </c>
@@ -2520,285 +2520,285 @@
       </c>
     </row>
     <row r="3" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A3" s="21" t="s">
+      <c r="A3" s="32" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="22"/>
-      <c r="C3" s="31" t="s">
+      <c r="B3" s="29"/>
+      <c r="C3" s="27" t="s">
         <v>28</v>
       </c>
-      <c r="D3" s="30"/>
-      <c r="E3" s="30"/>
-      <c r="F3" s="30"/>
-      <c r="G3" s="22"/>
+      <c r="D3" s="28"/>
+      <c r="E3" s="28"/>
+      <c r="F3" s="28"/>
+      <c r="G3" s="29"/>
     </row>
     <row r="4" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A4" s="21" t="s">
+      <c r="A4" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="22"/>
-      <c r="C4" s="32">
+      <c r="B4" s="29"/>
+      <c r="C4" s="42">
         <v>45789</v>
       </c>
-      <c r="D4" s="30"/>
-      <c r="E4" s="30"/>
-      <c r="F4" s="30"/>
-      <c r="G4" s="22"/>
+      <c r="D4" s="28"/>
+      <c r="E4" s="28"/>
+      <c r="F4" s="28"/>
+      <c r="G4" s="29"/>
     </row>
     <row r="5" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A5" s="21" t="s">
+      <c r="A5" s="32" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="22"/>
-      <c r="C5" s="31" t="s">
+      <c r="B5" s="29"/>
+      <c r="C5" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="D5" s="30"/>
-      <c r="E5" s="30"/>
-      <c r="F5" s="30"/>
-      <c r="G5" s="22"/>
+      <c r="D5" s="28"/>
+      <c r="E5" s="28"/>
+      <c r="F5" s="28"/>
+      <c r="G5" s="29"/>
     </row>
     <row r="6" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A6" s="23" t="s">
+      <c r="A6" s="35" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="24"/>
+      <c r="B6" s="36"/>
       <c r="C6" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D6" s="31" t="s">
+      <c r="D6" s="27" t="s">
         <v>101</v>
       </c>
-      <c r="E6" s="30"/>
-      <c r="F6" s="30"/>
-      <c r="G6" s="22"/>
+      <c r="E6" s="28"/>
+      <c r="F6" s="28"/>
+      <c r="G6" s="29"/>
     </row>
     <row r="7" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A7" s="25"/>
-      <c r="B7" s="26"/>
+      <c r="A7" s="39"/>
+      <c r="B7" s="40"/>
       <c r="C7" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D7" s="31"/>
-      <c r="E7" s="30"/>
-      <c r="F7" s="30"/>
-      <c r="G7" s="22"/>
+      <c r="D7" s="27"/>
+      <c r="E7" s="28"/>
+      <c r="F7" s="28"/>
+      <c r="G7" s="29"/>
     </row>
     <row r="8" spans="1:7" ht="47.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="27" t="s">
+      <c r="A8" s="41" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="22"/>
-      <c r="C8" s="36" t="s">
+      <c r="B8" s="29"/>
+      <c r="C8" s="30" t="s">
         <v>102</v>
       </c>
-      <c r="D8" s="30"/>
-      <c r="E8" s="30"/>
-      <c r="F8" s="30"/>
-      <c r="G8" s="22"/>
+      <c r="D8" s="28"/>
+      <c r="E8" s="28"/>
+      <c r="F8" s="28"/>
+      <c r="G8" s="29"/>
     </row>
     <row r="9" spans="1:7" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="27" t="s">
+      <c r="A9" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="22"/>
-      <c r="C9" s="36" t="s">
+      <c r="B9" s="29"/>
+      <c r="C9" s="30" t="s">
         <v>103</v>
       </c>
-      <c r="D9" s="30"/>
-      <c r="E9" s="30"/>
-      <c r="F9" s="30"/>
-      <c r="G9" s="22"/>
+      <c r="D9" s="28"/>
+      <c r="E9" s="28"/>
+      <c r="F9" s="28"/>
+      <c r="G9" s="29"/>
     </row>
     <row r="10" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A10" s="41" t="s">
+      <c r="A10" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="B10" s="42"/>
+      <c r="B10" s="47"/>
       <c r="C10" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D10" s="66" t="s">
+      <c r="D10" s="69" t="s">
         <v>18</v>
       </c>
-      <c r="E10" s="67"/>
-      <c r="F10" s="66" t="s">
+      <c r="E10" s="70"/>
+      <c r="F10" s="69" t="s">
         <v>18</v>
       </c>
-      <c r="G10" s="67"/>
+      <c r="G10" s="70"/>
     </row>
     <row r="11" spans="1:7" ht="58.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="43"/>
-      <c r="B11" s="44"/>
-      <c r="C11" s="71">
+      <c r="A11" s="48"/>
+      <c r="B11" s="49"/>
+      <c r="C11" s="21">
         <v>1</v>
       </c>
-      <c r="D11" s="69" t="s">
+      <c r="D11" s="67" t="s">
         <v>208</v>
       </c>
-      <c r="E11" s="70"/>
-      <c r="F11" s="70"/>
-      <c r="G11" s="70"/>
+      <c r="E11" s="68"/>
+      <c r="F11" s="68"/>
+      <c r="G11" s="68"/>
     </row>
     <row r="12" spans="1:7" ht="58.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="43"/>
-      <c r="B12" s="44"/>
-      <c r="C12" s="71">
+      <c r="A12" s="48"/>
+      <c r="B12" s="49"/>
+      <c r="C12" s="21">
         <v>2</v>
       </c>
-      <c r="D12" s="70"/>
-      <c r="E12" s="70"/>
-      <c r="F12" s="69" t="s">
+      <c r="D12" s="68"/>
+      <c r="E12" s="68"/>
+      <c r="F12" s="67" t="s">
         <v>209</v>
       </c>
-      <c r="G12" s="70"/>
+      <c r="G12" s="68"/>
     </row>
     <row r="13" spans="1:7" ht="58.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="43"/>
-      <c r="B13" s="44"/>
-      <c r="C13" s="71">
+      <c r="A13" s="48"/>
+      <c r="B13" s="49"/>
+      <c r="C13" s="21">
         <v>3</v>
       </c>
-      <c r="D13" s="70"/>
-      <c r="E13" s="70"/>
-      <c r="F13" s="69" t="s">
+      <c r="D13" s="68"/>
+      <c r="E13" s="68"/>
+      <c r="F13" s="67" t="s">
         <v>210</v>
       </c>
-      <c r="G13" s="70"/>
+      <c r="G13" s="68"/>
     </row>
     <row r="14" spans="1:7" ht="58.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="43"/>
-      <c r="B14" s="44"/>
-      <c r="C14" s="71">
+      <c r="A14" s="48"/>
+      <c r="B14" s="49"/>
+      <c r="C14" s="21">
         <v>4</v>
       </c>
-      <c r="D14" s="69" t="s">
+      <c r="D14" s="67" t="s">
         <v>211</v>
       </c>
-      <c r="E14" s="70"/>
-      <c r="F14" s="70"/>
-      <c r="G14" s="70"/>
+      <c r="E14" s="68"/>
+      <c r="F14" s="68"/>
+      <c r="G14" s="68"/>
     </row>
     <row r="15" spans="1:7" ht="58.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="43"/>
-      <c r="B15" s="44"/>
-      <c r="C15" s="71">
+      <c r="A15" s="48"/>
+      <c r="B15" s="49"/>
+      <c r="C15" s="21">
         <v>5</v>
       </c>
-      <c r="D15" s="69" t="s">
+      <c r="D15" s="67" t="s">
         <v>212</v>
       </c>
-      <c r="E15" s="70"/>
-      <c r="F15" s="69" t="s">
+      <c r="E15" s="68"/>
+      <c r="F15" s="67" t="s">
         <v>213</v>
       </c>
-      <c r="G15" s="70"/>
+      <c r="G15" s="68"/>
     </row>
     <row r="16" spans="1:7" ht="58.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="43"/>
-      <c r="B16" s="44"/>
-      <c r="C16" s="71">
+      <c r="A16" s="48"/>
+      <c r="B16" s="49"/>
+      <c r="C16" s="21">
         <v>6</v>
       </c>
-      <c r="D16" s="69" t="s">
+      <c r="D16" s="67" t="s">
         <v>214</v>
       </c>
-      <c r="E16" s="70"/>
-      <c r="F16" s="70"/>
-      <c r="G16" s="70"/>
+      <c r="E16" s="68"/>
+      <c r="F16" s="68"/>
+      <c r="G16" s="68"/>
     </row>
     <row r="17" spans="1:7" ht="58.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="43"/>
-      <c r="B17" s="44"/>
-      <c r="C17" s="71">
+      <c r="A17" s="48"/>
+      <c r="B17" s="49"/>
+      <c r="C17" s="21">
         <v>7</v>
       </c>
-      <c r="D17" s="69" t="s">
+      <c r="D17" s="67" t="s">
         <v>215</v>
       </c>
-      <c r="E17" s="70"/>
-      <c r="F17" s="70"/>
-      <c r="G17" s="70"/>
+      <c r="E17" s="68"/>
+      <c r="F17" s="68"/>
+      <c r="G17" s="68"/>
     </row>
     <row r="18" spans="1:7" ht="58.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="43"/>
-      <c r="B18" s="44"/>
-      <c r="C18" s="71">
+      <c r="A18" s="48"/>
+      <c r="B18" s="49"/>
+      <c r="C18" s="21">
         <v>8</v>
       </c>
-      <c r="D18" s="70"/>
-      <c r="E18" s="70"/>
-      <c r="F18" s="69" t="s">
+      <c r="D18" s="68"/>
+      <c r="E18" s="68"/>
+      <c r="F18" s="67" t="s">
         <v>216</v>
       </c>
-      <c r="G18" s="70"/>
+      <c r="G18" s="68"/>
     </row>
     <row r="19" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="23" t="s">
+      <c r="A19" s="35" t="s">
         <v>19</v>
       </c>
-      <c r="B19" s="24"/>
+      <c r="B19" s="36"/>
       <c r="C19" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D19" s="21" t="s">
+      <c r="D19" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="E19" s="30"/>
-      <c r="F19" s="30"/>
-      <c r="G19" s="22"/>
+      <c r="E19" s="28"/>
+      <c r="F19" s="28"/>
+      <c r="G19" s="29"/>
     </row>
     <row r="20" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="28"/>
-      <c r="B20" s="29"/>
+      <c r="A20" s="37"/>
+      <c r="B20" s="38"/>
       <c r="C20" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="D20" s="36" t="s">
+      <c r="D20" s="30" t="s">
         <v>105</v>
       </c>
-      <c r="E20" s="30"/>
-      <c r="F20" s="30"/>
-      <c r="G20" s="22"/>
+      <c r="E20" s="28"/>
+      <c r="F20" s="28"/>
+      <c r="G20" s="29"/>
     </row>
     <row r="21" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="28"/>
-      <c r="B21" s="29"/>
+      <c r="A21" s="37"/>
+      <c r="B21" s="38"/>
       <c r="C21" s="16" t="s">
         <v>108</v>
       </c>
-      <c r="D21" s="35" t="s">
+      <c r="D21" s="31" t="s">
         <v>106</v>
       </c>
-      <c r="E21" s="30"/>
-      <c r="F21" s="30"/>
-      <c r="G21" s="22"/>
+      <c r="E21" s="28"/>
+      <c r="F21" s="28"/>
+      <c r="G21" s="29"/>
     </row>
     <row r="22" spans="1:7" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="25"/>
-      <c r="B22" s="26"/>
+      <c r="A22" s="39"/>
+      <c r="B22" s="40"/>
       <c r="C22" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="D22" s="35" t="s">
+      <c r="D22" s="31" t="s">
         <v>107</v>
       </c>
-      <c r="E22" s="30"/>
-      <c r="F22" s="30"/>
-      <c r="G22" s="22"/>
+      <c r="E22" s="28"/>
+      <c r="F22" s="28"/>
+      <c r="G22" s="29"/>
     </row>
     <row r="23" spans="1:7" ht="60.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="27" t="s">
+      <c r="A23" s="41" t="s">
         <v>26</v>
       </c>
-      <c r="B23" s="22"/>
-      <c r="C23" s="36" t="s">
+      <c r="B23" s="29"/>
+      <c r="C23" s="30" t="s">
         <v>104</v>
       </c>
-      <c r="D23" s="30"/>
-      <c r="E23" s="30"/>
-      <c r="F23" s="30"/>
-      <c r="G23" s="22"/>
+      <c r="D23" s="28"/>
+      <c r="E23" s="28"/>
+      <c r="F23" s="28"/>
+      <c r="G23" s="29"/>
     </row>
     <row r="25" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="26" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -3497,6 +3497,33 @@
     <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="43">
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="A19:B22"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:G1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:E2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="C4:G4"/>
+    <mergeCell ref="D19:G19"/>
+    <mergeCell ref="D20:G20"/>
+    <mergeCell ref="D21:G21"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A6:B7"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="D22:G22"/>
+    <mergeCell ref="C23:G23"/>
+    <mergeCell ref="C5:G5"/>
+    <mergeCell ref="D6:G6"/>
+    <mergeCell ref="D7:G7"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="D17:E17"/>
     <mergeCell ref="A10:B18"/>
     <mergeCell ref="D10:E10"/>
     <mergeCell ref="F10:G10"/>
@@ -3513,33 +3540,6 @@
     <mergeCell ref="D16:E16"/>
     <mergeCell ref="F16:G16"/>
     <mergeCell ref="D18:E18"/>
-    <mergeCell ref="D22:G22"/>
-    <mergeCell ref="C23:G23"/>
-    <mergeCell ref="C5:G5"/>
-    <mergeCell ref="D6:G6"/>
-    <mergeCell ref="D7:G7"/>
-    <mergeCell ref="C8:G8"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="A19:B22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:G1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:E2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="C4:G4"/>
-    <mergeCell ref="D19:G19"/>
-    <mergeCell ref="D20:G20"/>
-    <mergeCell ref="D21:G21"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A6:B7"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="A9:B9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3557,28 +3557,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="21" t="s">
+      <c r="B1" s="29"/>
+      <c r="C1" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="22"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="29"/>
     </row>
     <row r="2" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="22"/>
-      <c r="C2" s="38" t="s">
+      <c r="B2" s="29"/>
+      <c r="C2" s="56" t="s">
         <v>112</v>
       </c>
-      <c r="D2" s="30"/>
-      <c r="E2" s="22"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="29"/>
       <c r="F2" s="1" t="s">
         <v>4</v>
       </c>
@@ -3587,270 +3587,270 @@
       </c>
     </row>
     <row r="3" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A3" s="21" t="s">
+      <c r="A3" s="32" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="22"/>
-      <c r="C3" s="31" t="s">
+      <c r="B3" s="29"/>
+      <c r="C3" s="27" t="s">
         <v>28</v>
       </c>
-      <c r="D3" s="30"/>
-      <c r="E3" s="30"/>
-      <c r="F3" s="30"/>
-      <c r="G3" s="22"/>
+      <c r="D3" s="28"/>
+      <c r="E3" s="28"/>
+      <c r="F3" s="28"/>
+      <c r="G3" s="29"/>
     </row>
     <row r="4" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A4" s="21" t="s">
+      <c r="A4" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="22"/>
-      <c r="C4" s="32">
+      <c r="B4" s="29"/>
+      <c r="C4" s="42">
         <v>45789</v>
       </c>
-      <c r="D4" s="30"/>
-      <c r="E4" s="30"/>
-      <c r="F4" s="30"/>
-      <c r="G4" s="22"/>
+      <c r="D4" s="28"/>
+      <c r="E4" s="28"/>
+      <c r="F4" s="28"/>
+      <c r="G4" s="29"/>
     </row>
     <row r="5" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A5" s="21" t="s">
+      <c r="A5" s="32" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="22"/>
-      <c r="C5" s="31" t="s">
+      <c r="B5" s="29"/>
+      <c r="C5" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="D5" s="30"/>
-      <c r="E5" s="30"/>
-      <c r="F5" s="30"/>
-      <c r="G5" s="22"/>
+      <c r="D5" s="28"/>
+      <c r="E5" s="28"/>
+      <c r="F5" s="28"/>
+      <c r="G5" s="29"/>
     </row>
     <row r="6" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A6" s="23" t="s">
+      <c r="A6" s="35" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="24"/>
+      <c r="B6" s="36"/>
       <c r="C6" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D6" s="38" t="s">
+      <c r="D6" s="56" t="s">
         <v>113</v>
       </c>
-      <c r="E6" s="30"/>
-      <c r="F6" s="30"/>
-      <c r="G6" s="22"/>
+      <c r="E6" s="28"/>
+      <c r="F6" s="28"/>
+      <c r="G6" s="29"/>
     </row>
     <row r="7" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A7" s="25"/>
-      <c r="B7" s="26"/>
+      <c r="A7" s="39"/>
+      <c r="B7" s="40"/>
       <c r="C7" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D7" s="31"/>
-      <c r="E7" s="30"/>
-      <c r="F7" s="30"/>
-      <c r="G7" s="22"/>
+      <c r="D7" s="27"/>
+      <c r="E7" s="28"/>
+      <c r="F7" s="28"/>
+      <c r="G7" s="29"/>
     </row>
     <row r="8" spans="1:7" ht="47.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="27" t="s">
+      <c r="A8" s="41" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="22"/>
-      <c r="C8" s="35" t="s">
+      <c r="B8" s="29"/>
+      <c r="C8" s="31" t="s">
         <v>114</v>
       </c>
-      <c r="D8" s="30"/>
-      <c r="E8" s="30"/>
-      <c r="F8" s="30"/>
-      <c r="G8" s="22"/>
+      <c r="D8" s="28"/>
+      <c r="E8" s="28"/>
+      <c r="F8" s="28"/>
+      <c r="G8" s="29"/>
     </row>
     <row r="9" spans="1:7" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="27" t="s">
+      <c r="A9" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="22"/>
-      <c r="C9" s="35" t="s">
+      <c r="B9" s="29"/>
+      <c r="C9" s="31" t="s">
         <v>115</v>
       </c>
-      <c r="D9" s="30"/>
-      <c r="E9" s="30"/>
-      <c r="F9" s="30"/>
-      <c r="G9" s="22"/>
+      <c r="D9" s="28"/>
+      <c r="E9" s="28"/>
+      <c r="F9" s="28"/>
+      <c r="G9" s="29"/>
     </row>
     <row r="10" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A10" s="41" t="s">
+      <c r="A10" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="B10" s="42"/>
+      <c r="B10" s="47"/>
       <c r="C10" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D10" s="66" t="s">
+      <c r="D10" s="69" t="s">
         <v>18</v>
       </c>
-      <c r="E10" s="67"/>
-      <c r="F10" s="66" t="s">
+      <c r="E10" s="70"/>
+      <c r="F10" s="69" t="s">
         <v>18</v>
       </c>
-      <c r="G10" s="67"/>
+      <c r="G10" s="70"/>
     </row>
     <row r="11" spans="1:7" ht="62.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="43"/>
-      <c r="B11" s="44"/>
-      <c r="C11" s="71">
+      <c r="A11" s="48"/>
+      <c r="B11" s="49"/>
+      <c r="C11" s="21">
         <v>1</v>
       </c>
-      <c r="D11" s="69" t="s">
+      <c r="D11" s="67" t="s">
         <v>217</v>
       </c>
-      <c r="E11" s="70"/>
-      <c r="F11" s="70"/>
-      <c r="G11" s="70"/>
+      <c r="E11" s="68"/>
+      <c r="F11" s="68"/>
+      <c r="G11" s="68"/>
     </row>
     <row r="12" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="43"/>
-      <c r="B12" s="44"/>
-      <c r="C12" s="71">
+      <c r="A12" s="48"/>
+      <c r="B12" s="49"/>
+      <c r="C12" s="21">
         <v>2</v>
       </c>
-      <c r="D12" s="70"/>
-      <c r="E12" s="70"/>
-      <c r="F12" s="69" t="s">
+      <c r="D12" s="68"/>
+      <c r="E12" s="68"/>
+      <c r="F12" s="67" t="s">
         <v>218</v>
       </c>
-      <c r="G12" s="70"/>
+      <c r="G12" s="68"/>
     </row>
     <row r="13" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="43"/>
-      <c r="B13" s="44"/>
-      <c r="C13" s="71">
+      <c r="A13" s="48"/>
+      <c r="B13" s="49"/>
+      <c r="C13" s="21">
         <v>3</v>
       </c>
-      <c r="D13" s="69" t="s">
+      <c r="D13" s="67" t="s">
         <v>219</v>
       </c>
-      <c r="E13" s="70"/>
-      <c r="F13" s="70"/>
-      <c r="G13" s="70"/>
+      <c r="E13" s="68"/>
+      <c r="F13" s="68"/>
+      <c r="G13" s="68"/>
     </row>
     <row r="14" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="43"/>
-      <c r="B14" s="44"/>
-      <c r="C14" s="71">
+      <c r="A14" s="48"/>
+      <c r="B14" s="49"/>
+      <c r="C14" s="21">
         <v>4</v>
       </c>
-      <c r="D14" s="69" t="s">
+      <c r="D14" s="67" t="s">
         <v>220</v>
       </c>
-      <c r="E14" s="70"/>
-      <c r="F14" s="70"/>
-      <c r="G14" s="70"/>
+      <c r="E14" s="68"/>
+      <c r="F14" s="68"/>
+      <c r="G14" s="68"/>
     </row>
     <row r="15" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="43"/>
-      <c r="B15" s="44"/>
-      <c r="C15" s="71">
+      <c r="A15" s="48"/>
+      <c r="B15" s="49"/>
+      <c r="C15" s="21">
         <v>5</v>
       </c>
-      <c r="D15" s="69" t="s">
+      <c r="D15" s="67" t="s">
         <v>221</v>
       </c>
-      <c r="E15" s="70"/>
-      <c r="F15" s="70"/>
-      <c r="G15" s="70"/>
+      <c r="E15" s="68"/>
+      <c r="F15" s="68"/>
+      <c r="G15" s="68"/>
     </row>
     <row r="16" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="43"/>
-      <c r="B16" s="44"/>
-      <c r="C16" s="71">
+      <c r="A16" s="48"/>
+      <c r="B16" s="49"/>
+      <c r="C16" s="21">
         <v>6</v>
       </c>
-      <c r="D16" s="70"/>
-      <c r="E16" s="70"/>
-      <c r="F16" s="69" t="s">
+      <c r="D16" s="68"/>
+      <c r="E16" s="68"/>
+      <c r="F16" s="67" t="s">
         <v>222</v>
       </c>
-      <c r="G16" s="70"/>
+      <c r="G16" s="68"/>
     </row>
     <row r="17" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="43"/>
-      <c r="B17" s="44"/>
-      <c r="C17" s="71">
+      <c r="A17" s="48"/>
+      <c r="B17" s="49"/>
+      <c r="C17" s="21">
         <v>7</v>
       </c>
-      <c r="D17" s="70"/>
-      <c r="E17" s="70"/>
-      <c r="F17" s="69" t="s">
+      <c r="D17" s="68"/>
+      <c r="E17" s="68"/>
+      <c r="F17" s="67" t="s">
         <v>223</v>
       </c>
-      <c r="G17" s="70"/>
+      <c r="G17" s="68"/>
     </row>
     <row r="18" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="23" t="s">
+      <c r="A18" s="35" t="s">
         <v>19</v>
       </c>
-      <c r="B18" s="24"/>
+      <c r="B18" s="36"/>
       <c r="C18" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D18" s="21" t="s">
+      <c r="D18" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="E18" s="30"/>
-      <c r="F18" s="30"/>
-      <c r="G18" s="22"/>
+      <c r="E18" s="28"/>
+      <c r="F18" s="28"/>
+      <c r="G18" s="29"/>
     </row>
     <row r="19" spans="1:7" ht="31.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="28"/>
-      <c r="B19" s="29"/>
+      <c r="A19" s="37"/>
+      <c r="B19" s="38"/>
       <c r="C19" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="D19" s="35" t="s">
+      <c r="D19" s="31" t="s">
         <v>117</v>
       </c>
-      <c r="E19" s="30"/>
-      <c r="F19" s="30"/>
-      <c r="G19" s="22"/>
+      <c r="E19" s="28"/>
+      <c r="F19" s="28"/>
+      <c r="G19" s="29"/>
     </row>
     <row r="20" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="28"/>
-      <c r="B20" s="29"/>
+      <c r="A20" s="37"/>
+      <c r="B20" s="38"/>
       <c r="C20" s="16" t="s">
         <v>74</v>
       </c>
-      <c r="D20" s="35" t="s">
+      <c r="D20" s="31" t="s">
         <v>118</v>
       </c>
-      <c r="E20" s="30"/>
-      <c r="F20" s="30"/>
-      <c r="G20" s="22"/>
+      <c r="E20" s="28"/>
+      <c r="F20" s="28"/>
+      <c r="G20" s="29"/>
     </row>
     <row r="21" spans="1:7" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="25"/>
-      <c r="B21" s="26"/>
+      <c r="A21" s="39"/>
+      <c r="B21" s="40"/>
       <c r="C21" s="16" t="s">
         <v>75</v>
       </c>
-      <c r="D21" s="35" t="s">
+      <c r="D21" s="31" t="s">
         <v>119</v>
       </c>
-      <c r="E21" s="30"/>
-      <c r="F21" s="30"/>
-      <c r="G21" s="22"/>
+      <c r="E21" s="28"/>
+      <c r="F21" s="28"/>
+      <c r="G21" s="29"/>
     </row>
     <row r="22" spans="1:7" ht="46.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="27" t="s">
+      <c r="A22" s="41" t="s">
         <v>26</v>
       </c>
-      <c r="B22" s="22"/>
-      <c r="C22" s="35" t="s">
+      <c r="B22" s="29"/>
+      <c r="C22" s="31" t="s">
         <v>116</v>
       </c>
-      <c r="D22" s="30"/>
-      <c r="E22" s="30"/>
-      <c r="F22" s="30"/>
-      <c r="G22" s="22"/>
+      <c r="D22" s="28"/>
+      <c r="E22" s="28"/>
+      <c r="F22" s="28"/>
+      <c r="G22" s="29"/>
     </row>
     <row r="24" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="25" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -4549,25 +4549,13 @@
     <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="41">
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:G1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:E2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="C4:G4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C5:G5"/>
-    <mergeCell ref="A6:B7"/>
-    <mergeCell ref="D6:G6"/>
-    <mergeCell ref="D7:G7"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:G22"/>
+    <mergeCell ref="A18:B21"/>
+    <mergeCell ref="D18:G18"/>
+    <mergeCell ref="D19:G19"/>
+    <mergeCell ref="D20:G20"/>
+    <mergeCell ref="D21:G21"/>
     <mergeCell ref="A8:B8"/>
     <mergeCell ref="C8:G8"/>
     <mergeCell ref="A9:B9"/>
@@ -4579,17 +4567,29 @@
     <mergeCell ref="F11:G11"/>
     <mergeCell ref="D12:E12"/>
     <mergeCell ref="F12:G12"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:G22"/>
-    <mergeCell ref="A18:B21"/>
-    <mergeCell ref="D18:G18"/>
-    <mergeCell ref="D19:G19"/>
-    <mergeCell ref="D20:G20"/>
-    <mergeCell ref="D21:G21"/>
     <mergeCell ref="D16:E16"/>
     <mergeCell ref="F16:G16"/>
     <mergeCell ref="D17:E17"/>
     <mergeCell ref="F17:G17"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:G4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C5:G5"/>
+    <mergeCell ref="A6:B7"/>
+    <mergeCell ref="D6:G6"/>
+    <mergeCell ref="D7:G7"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:G1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:E2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="F15:G15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -4610,28 +4610,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="21" t="s">
+      <c r="B1" s="29"/>
+      <c r="C1" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="22"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="29"/>
     </row>
     <row r="2" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="22"/>
-      <c r="C2" s="38" t="s">
+      <c r="B2" s="29"/>
+      <c r="C2" s="56" t="s">
         <v>120</v>
       </c>
-      <c r="D2" s="30"/>
-      <c r="E2" s="22"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="29"/>
       <c r="F2" s="1" t="s">
         <v>4</v>
       </c>
@@ -4640,272 +4640,272 @@
       </c>
     </row>
     <row r="3" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A3" s="21" t="s">
+      <c r="A3" s="32" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="22"/>
-      <c r="C3" s="31" t="s">
+      <c r="B3" s="29"/>
+      <c r="C3" s="27" t="s">
         <v>28</v>
       </c>
-      <c r="D3" s="30"/>
-      <c r="E3" s="30"/>
-      <c r="F3" s="30"/>
-      <c r="G3" s="22"/>
+      <c r="D3" s="28"/>
+      <c r="E3" s="28"/>
+      <c r="F3" s="28"/>
+      <c r="G3" s="29"/>
     </row>
     <row r="4" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A4" s="21" t="s">
+      <c r="A4" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="22"/>
-      <c r="C4" s="32">
+      <c r="B4" s="29"/>
+      <c r="C4" s="42">
         <v>45789</v>
       </c>
-      <c r="D4" s="30"/>
-      <c r="E4" s="30"/>
-      <c r="F4" s="30"/>
-      <c r="G4" s="22"/>
+      <c r="D4" s="28"/>
+      <c r="E4" s="28"/>
+      <c r="F4" s="28"/>
+      <c r="G4" s="29"/>
     </row>
     <row r="5" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A5" s="21" t="s">
+      <c r="A5" s="32" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="22"/>
-      <c r="C5" s="31" t="s">
+      <c r="B5" s="29"/>
+      <c r="C5" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="D5" s="30"/>
-      <c r="E5" s="30"/>
-      <c r="F5" s="30"/>
-      <c r="G5" s="22"/>
+      <c r="D5" s="28"/>
+      <c r="E5" s="28"/>
+      <c r="F5" s="28"/>
+      <c r="G5" s="29"/>
     </row>
     <row r="6" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A6" s="23" t="s">
+      <c r="A6" s="35" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="24"/>
+      <c r="B6" s="36"/>
       <c r="C6" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D6" s="38" t="s">
+      <c r="D6" s="56" t="s">
         <v>66</v>
       </c>
-      <c r="E6" s="30"/>
-      <c r="F6" s="30"/>
-      <c r="G6" s="22"/>
+      <c r="E6" s="28"/>
+      <c r="F6" s="28"/>
+      <c r="G6" s="29"/>
     </row>
     <row r="7" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A7" s="25"/>
-      <c r="B7" s="26"/>
+      <c r="A7" s="39"/>
+      <c r="B7" s="40"/>
       <c r="C7" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D7" s="31"/>
-      <c r="E7" s="30"/>
-      <c r="F7" s="30"/>
-      <c r="G7" s="22"/>
+      <c r="D7" s="27"/>
+      <c r="E7" s="28"/>
+      <c r="F7" s="28"/>
+      <c r="G7" s="29"/>
     </row>
     <row r="8" spans="1:7" ht="47.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="27" t="s">
+      <c r="A8" s="41" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="22"/>
-      <c r="C8" s="35" t="s">
+      <c r="B8" s="29"/>
+      <c r="C8" s="31" t="s">
         <v>121</v>
       </c>
-      <c r="D8" s="30"/>
-      <c r="E8" s="30"/>
-      <c r="F8" s="30"/>
-      <c r="G8" s="22"/>
+      <c r="D8" s="28"/>
+      <c r="E8" s="28"/>
+      <c r="F8" s="28"/>
+      <c r="G8" s="29"/>
     </row>
     <row r="9" spans="1:7" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="27" t="s">
+      <c r="A9" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="22"/>
-      <c r="C9" s="35" t="s">
+      <c r="B9" s="29"/>
+      <c r="C9" s="31" t="s">
         <v>122</v>
       </c>
-      <c r="D9" s="30"/>
-      <c r="E9" s="30"/>
-      <c r="F9" s="30"/>
-      <c r="G9" s="22"/>
+      <c r="D9" s="28"/>
+      <c r="E9" s="28"/>
+      <c r="F9" s="28"/>
+      <c r="G9" s="29"/>
     </row>
     <row r="10" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A10" s="41" t="s">
+      <c r="A10" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="B10" s="42"/>
+      <c r="B10" s="47"/>
       <c r="C10" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D10" s="66" t="s">
+      <c r="D10" s="69" t="s">
         <v>18</v>
       </c>
-      <c r="E10" s="67"/>
-      <c r="F10" s="66" t="s">
+      <c r="E10" s="70"/>
+      <c r="F10" s="69" t="s">
         <v>18</v>
       </c>
-      <c r="G10" s="67"/>
+      <c r="G10" s="70"/>
     </row>
     <row r="11" spans="1:7" ht="63.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="43"/>
-      <c r="B11" s="44"/>
-      <c r="C11" s="71">
+      <c r="A11" s="48"/>
+      <c r="B11" s="49"/>
+      <c r="C11" s="21">
         <v>1</v>
       </c>
-      <c r="D11" s="69" t="s">
+      <c r="D11" s="67" t="s">
         <v>224</v>
       </c>
-      <c r="E11" s="70"/>
-      <c r="F11" s="70"/>
-      <c r="G11" s="70"/>
+      <c r="E11" s="68"/>
+      <c r="F11" s="68"/>
+      <c r="G11" s="68"/>
     </row>
     <row r="12" spans="1:7" ht="63.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="43"/>
-      <c r="B12" s="44"/>
-      <c r="C12" s="71">
+      <c r="A12" s="48"/>
+      <c r="B12" s="49"/>
+      <c r="C12" s="21">
         <v>2</v>
       </c>
-      <c r="D12" s="69" t="s">
+      <c r="D12" s="67" t="s">
         <v>225</v>
       </c>
-      <c r="E12" s="70"/>
-      <c r="F12" s="69" t="s">
+      <c r="E12" s="68"/>
+      <c r="F12" s="67" t="s">
         <v>226</v>
       </c>
-      <c r="G12" s="70"/>
+      <c r="G12" s="68"/>
     </row>
     <row r="13" spans="1:7" ht="63.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="43"/>
-      <c r="B13" s="44"/>
-      <c r="C13" s="71">
+      <c r="A13" s="48"/>
+      <c r="B13" s="49"/>
+      <c r="C13" s="21">
         <v>3</v>
       </c>
-      <c r="D13" s="69" t="s">
+      <c r="D13" s="67" t="s">
         <v>227</v>
       </c>
-      <c r="E13" s="70"/>
-      <c r="F13" s="70"/>
-      <c r="G13" s="70"/>
+      <c r="E13" s="68"/>
+      <c r="F13" s="68"/>
+      <c r="G13" s="68"/>
     </row>
     <row r="14" spans="1:7" ht="63.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="43"/>
-      <c r="B14" s="44"/>
-      <c r="C14" s="71">
+      <c r="A14" s="48"/>
+      <c r="B14" s="49"/>
+      <c r="C14" s="21">
         <v>4</v>
       </c>
-      <c r="D14" s="69" t="s">
+      <c r="D14" s="67" t="s">
         <v>228</v>
       </c>
-      <c r="E14" s="70"/>
-      <c r="F14" s="70"/>
-      <c r="G14" s="70"/>
+      <c r="E14" s="68"/>
+      <c r="F14" s="68"/>
+      <c r="G14" s="68"/>
     </row>
     <row r="15" spans="1:7" ht="63.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="43"/>
-      <c r="B15" s="44"/>
-      <c r="C15" s="71">
+      <c r="A15" s="48"/>
+      <c r="B15" s="49"/>
+      <c r="C15" s="21">
         <v>5</v>
       </c>
-      <c r="D15" s="70"/>
-      <c r="E15" s="70"/>
-      <c r="F15" s="69" t="s">
+      <c r="D15" s="68"/>
+      <c r="E15" s="68"/>
+      <c r="F15" s="67" t="s">
         <v>229</v>
       </c>
-      <c r="G15" s="70"/>
+      <c r="G15" s="68"/>
     </row>
     <row r="16" spans="1:7" ht="63.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="43"/>
-      <c r="B16" s="44"/>
-      <c r="C16" s="71">
+      <c r="A16" s="48"/>
+      <c r="B16" s="49"/>
+      <c r="C16" s="21">
         <v>6</v>
       </c>
-      <c r="D16" s="70"/>
-      <c r="E16" s="70"/>
-      <c r="F16" s="69" t="s">
+      <c r="D16" s="68"/>
+      <c r="E16" s="68"/>
+      <c r="F16" s="67" t="s">
         <v>230</v>
       </c>
-      <c r="G16" s="70"/>
+      <c r="G16" s="68"/>
     </row>
     <row r="17" spans="1:7" ht="63.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="43"/>
-      <c r="B17" s="44"/>
-      <c r="C17" s="71">
+      <c r="A17" s="48"/>
+      <c r="B17" s="49"/>
+      <c r="C17" s="21">
         <v>7</v>
       </c>
-      <c r="D17" s="70"/>
-      <c r="E17" s="70"/>
-      <c r="F17" s="69" t="s">
+      <c r="D17" s="68"/>
+      <c r="E17" s="68"/>
+      <c r="F17" s="67" t="s">
         <v>231</v>
       </c>
-      <c r="G17" s="70"/>
+      <c r="G17" s="68"/>
     </row>
     <row r="18" spans="1:7" ht="63.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="43"/>
-      <c r="B18" s="44"/>
-      <c r="C18" s="71">
+      <c r="A18" s="48"/>
+      <c r="B18" s="49"/>
+      <c r="C18" s="21">
         <v>8</v>
       </c>
-      <c r="D18" s="70"/>
-      <c r="E18" s="70"/>
-      <c r="F18" s="69" t="s">
+      <c r="D18" s="68"/>
+      <c r="E18" s="68"/>
+      <c r="F18" s="67" t="s">
         <v>232</v>
       </c>
-      <c r="G18" s="70"/>
+      <c r="G18" s="68"/>
     </row>
     <row r="19" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="23" t="s">
+      <c r="A19" s="35" t="s">
         <v>19</v>
       </c>
-      <c r="B19" s="24"/>
+      <c r="B19" s="36"/>
       <c r="C19" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D19" s="21" t="s">
+      <c r="D19" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="E19" s="30"/>
-      <c r="F19" s="30"/>
-      <c r="G19" s="22"/>
+      <c r="E19" s="28"/>
+      <c r="F19" s="28"/>
+      <c r="G19" s="29"/>
     </row>
     <row r="20" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="28"/>
-      <c r="B20" s="29"/>
+      <c r="A20" s="37"/>
+      <c r="B20" s="38"/>
       <c r="C20" s="16" t="s">
         <v>126</v>
       </c>
-      <c r="D20" s="35" t="s">
+      <c r="D20" s="31" t="s">
         <v>124</v>
       </c>
-      <c r="E20" s="30"/>
-      <c r="F20" s="30"/>
-      <c r="G20" s="22"/>
+      <c r="E20" s="28"/>
+      <c r="F20" s="28"/>
+      <c r="G20" s="29"/>
     </row>
     <row r="21" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="28"/>
-      <c r="B21" s="29"/>
+      <c r="A21" s="37"/>
+      <c r="B21" s="38"/>
       <c r="C21" s="16" t="s">
         <v>99</v>
       </c>
-      <c r="D21" s="35" t="s">
+      <c r="D21" s="31" t="s">
         <v>125</v>
       </c>
-      <c r="E21" s="30"/>
-      <c r="F21" s="30"/>
-      <c r="G21" s="22"/>
+      <c r="E21" s="28"/>
+      <c r="F21" s="28"/>
+      <c r="G21" s="29"/>
     </row>
     <row r="22" spans="1:7" ht="60.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="27" t="s">
+      <c r="A22" s="41" t="s">
         <v>26</v>
       </c>
-      <c r="B22" s="22"/>
-      <c r="C22" s="35" t="s">
+      <c r="B22" s="29"/>
+      <c r="C22" s="31" t="s">
         <v>123</v>
       </c>
-      <c r="D22" s="30"/>
-      <c r="E22" s="30"/>
-      <c r="F22" s="30"/>
-      <c r="G22" s="22"/>
+      <c r="D22" s="28"/>
+      <c r="E22" s="28"/>
+      <c r="F22" s="28"/>
+      <c r="G22" s="29"/>
     </row>
     <row r="24" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="25" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -5604,25 +5604,13 @@
     <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="42">
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:G1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:E2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="C4:G4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C5:G5"/>
-    <mergeCell ref="A6:B7"/>
-    <mergeCell ref="D6:G6"/>
-    <mergeCell ref="D7:G7"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:G22"/>
+    <mergeCell ref="A19:B21"/>
+    <mergeCell ref="D19:G19"/>
+    <mergeCell ref="D20:G20"/>
+    <mergeCell ref="D21:G21"/>
     <mergeCell ref="A8:B8"/>
     <mergeCell ref="C8:G8"/>
     <mergeCell ref="A9:B9"/>
@@ -5634,18 +5622,30 @@
     <mergeCell ref="F11:G11"/>
     <mergeCell ref="D12:E12"/>
     <mergeCell ref="F12:G12"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:G22"/>
-    <mergeCell ref="A19:B21"/>
-    <mergeCell ref="D19:G19"/>
-    <mergeCell ref="D20:G20"/>
-    <mergeCell ref="D21:G21"/>
     <mergeCell ref="D16:E16"/>
     <mergeCell ref="F16:G16"/>
     <mergeCell ref="D17:E17"/>
     <mergeCell ref="F17:G17"/>
     <mergeCell ref="D18:E18"/>
-    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:G4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C5:G5"/>
+    <mergeCell ref="A6:B7"/>
+    <mergeCell ref="D6:G6"/>
+    <mergeCell ref="D7:G7"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:G1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:E2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="F15:G15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -5666,28 +5666,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="21" t="s">
+      <c r="B1" s="29"/>
+      <c r="C1" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="22"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="29"/>
     </row>
     <row r="2" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="22"/>
-      <c r="C2" s="38" t="s">
+      <c r="B2" s="29"/>
+      <c r="C2" s="56" t="s">
         <v>127</v>
       </c>
-      <c r="D2" s="30"/>
-      <c r="E2" s="22"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="29"/>
       <c r="F2" s="1" t="s">
         <v>4</v>
       </c>
@@ -5696,116 +5696,116 @@
       </c>
     </row>
     <row r="3" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A3" s="21" t="s">
+      <c r="A3" s="32" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="22"/>
-      <c r="C3" s="31" t="s">
+      <c r="B3" s="29"/>
+      <c r="C3" s="27" t="s">
         <v>28</v>
       </c>
-      <c r="D3" s="30"/>
-      <c r="E3" s="30"/>
-      <c r="F3" s="30"/>
-      <c r="G3" s="22"/>
+      <c r="D3" s="28"/>
+      <c r="E3" s="28"/>
+      <c r="F3" s="28"/>
+      <c r="G3" s="29"/>
     </row>
     <row r="4" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A4" s="21" t="s">
+      <c r="A4" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="22"/>
-      <c r="C4" s="32">
+      <c r="B4" s="29"/>
+      <c r="C4" s="42">
         <v>45789</v>
       </c>
-      <c r="D4" s="30"/>
-      <c r="E4" s="30"/>
-      <c r="F4" s="30"/>
-      <c r="G4" s="22"/>
+      <c r="D4" s="28"/>
+      <c r="E4" s="28"/>
+      <c r="F4" s="28"/>
+      <c r="G4" s="29"/>
     </row>
     <row r="5" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A5" s="21" t="s">
+      <c r="A5" s="32" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="22"/>
-      <c r="C5" s="31" t="s">
+      <c r="B5" s="29"/>
+      <c r="C5" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="D5" s="30"/>
-      <c r="E5" s="30"/>
-      <c r="F5" s="30"/>
-      <c r="G5" s="22"/>
+      <c r="D5" s="28"/>
+      <c r="E5" s="28"/>
+      <c r="F5" s="28"/>
+      <c r="G5" s="29"/>
     </row>
     <row r="6" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A6" s="23" t="s">
+      <c r="A6" s="35" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="24"/>
+      <c r="B6" s="36"/>
       <c r="C6" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D6" s="38" t="s">
+      <c r="D6" s="56" t="s">
         <v>101</v>
       </c>
-      <c r="E6" s="30"/>
-      <c r="F6" s="30"/>
-      <c r="G6" s="22"/>
+      <c r="E6" s="28"/>
+      <c r="F6" s="28"/>
+      <c r="G6" s="29"/>
     </row>
     <row r="7" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A7" s="25"/>
-      <c r="B7" s="26"/>
+      <c r="A7" s="39"/>
+      <c r="B7" s="40"/>
       <c r="C7" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D7" s="31"/>
-      <c r="E7" s="30"/>
-      <c r="F7" s="30"/>
-      <c r="G7" s="22"/>
+      <c r="D7" s="27"/>
+      <c r="E7" s="28"/>
+      <c r="F7" s="28"/>
+      <c r="G7" s="29"/>
     </row>
     <row r="8" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="27" t="s">
+      <c r="A8" s="41" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="22"/>
-      <c r="C8" s="35" t="s">
+      <c r="B8" s="29"/>
+      <c r="C8" s="31" t="s">
         <v>128</v>
       </c>
-      <c r="D8" s="30"/>
-      <c r="E8" s="30"/>
-      <c r="F8" s="30"/>
-      <c r="G8" s="22"/>
+      <c r="D8" s="28"/>
+      <c r="E8" s="28"/>
+      <c r="F8" s="28"/>
+      <c r="G8" s="29"/>
     </row>
     <row r="9" spans="1:7" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="27" t="s">
+      <c r="A9" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="22"/>
-      <c r="C9" s="36" t="s">
+      <c r="B9" s="29"/>
+      <c r="C9" s="30" t="s">
         <v>103</v>
       </c>
-      <c r="D9" s="30"/>
-      <c r="E9" s="30"/>
-      <c r="F9" s="30"/>
-      <c r="G9" s="22"/>
+      <c r="D9" s="28"/>
+      <c r="E9" s="28"/>
+      <c r="F9" s="28"/>
+      <c r="G9" s="29"/>
     </row>
     <row r="10" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A10" s="41" t="s">
+      <c r="A10" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="B10" s="42"/>
+      <c r="B10" s="47"/>
       <c r="C10" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D10" s="56" t="s">
+      <c r="D10" s="50" t="s">
         <v>18</v>
       </c>
-      <c r="E10" s="65"/>
-      <c r="F10" s="66" t="s">
+      <c r="E10" s="62"/>
+      <c r="F10" s="69" t="s">
         <v>18</v>
       </c>
-      <c r="G10" s="67"/>
+      <c r="G10" s="70"/>
     </row>
     <row r="11" spans="1:7" ht="58.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="43"/>
-      <c r="B11" s="44"/>
+      <c r="A11" s="48"/>
+      <c r="B11" s="49"/>
       <c r="C11" s="13">
         <v>1</v>
       </c>
@@ -5817,8 +5817,8 @@
       <c r="G11" s="73"/>
     </row>
     <row r="12" spans="1:7" ht="58.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="43"/>
-      <c r="B12" s="44"/>
+      <c r="A12" s="48"/>
+      <c r="B12" s="49"/>
       <c r="C12" s="13">
         <v>2</v>
       </c>
@@ -5830,8 +5830,8 @@
       <c r="G12" s="73"/>
     </row>
     <row r="13" spans="1:7" ht="58.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="43"/>
-      <c r="B13" s="44"/>
+      <c r="A13" s="48"/>
+      <c r="B13" s="49"/>
       <c r="C13" s="13">
         <v>3</v>
       </c>
@@ -5843,8 +5843,8 @@
       <c r="G13" s="73"/>
     </row>
     <row r="14" spans="1:7" ht="58.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="43"/>
-      <c r="B14" s="44"/>
+      <c r="A14" s="48"/>
+      <c r="B14" s="49"/>
       <c r="C14" s="13">
         <v>4</v>
       </c>
@@ -5858,8 +5858,8 @@
       <c r="G14" s="73"/>
     </row>
     <row r="15" spans="1:7" ht="58.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="43"/>
-      <c r="B15" s="44"/>
+      <c r="A15" s="48"/>
+      <c r="B15" s="49"/>
       <c r="C15" s="13">
         <v>5</v>
       </c>
@@ -5871,8 +5871,8 @@
       <c r="G15" s="73"/>
     </row>
     <row r="16" spans="1:7" ht="58.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="43"/>
-      <c r="B16" s="44"/>
+      <c r="A16" s="48"/>
+      <c r="B16" s="49"/>
       <c r="C16" s="13">
         <v>6</v>
       </c>
@@ -5884,58 +5884,58 @@
       <c r="G16" s="73"/>
     </row>
     <row r="17" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="23" t="s">
+      <c r="A17" s="35" t="s">
         <v>19</v>
       </c>
-      <c r="B17" s="24"/>
+      <c r="B17" s="36"/>
       <c r="C17" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D17" s="21" t="s">
+      <c r="D17" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="E17" s="30"/>
-      <c r="F17" s="30"/>
-      <c r="G17" s="22"/>
+      <c r="E17" s="28"/>
+      <c r="F17" s="28"/>
+      <c r="G17" s="29"/>
     </row>
     <row r="18" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="28"/>
-      <c r="B18" s="29"/>
+      <c r="A18" s="37"/>
+      <c r="B18" s="38"/>
       <c r="C18" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="D18" s="35" t="s">
+      <c r="D18" s="31" t="s">
         <v>129</v>
       </c>
-      <c r="E18" s="30"/>
-      <c r="F18" s="30"/>
-      <c r="G18" s="22"/>
+      <c r="E18" s="28"/>
+      <c r="F18" s="28"/>
+      <c r="G18" s="29"/>
     </row>
     <row r="19" spans="1:7" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="28"/>
-      <c r="B19" s="29"/>
+      <c r="A19" s="37"/>
+      <c r="B19" s="38"/>
       <c r="C19" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="D19" s="35" t="s">
+      <c r="D19" s="31" t="s">
         <v>130</v>
       </c>
-      <c r="E19" s="30"/>
-      <c r="F19" s="30"/>
-      <c r="G19" s="22"/>
+      <c r="E19" s="28"/>
+      <c r="F19" s="28"/>
+      <c r="G19" s="29"/>
     </row>
     <row r="20" spans="1:7" ht="60.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="27" t="s">
+      <c r="A20" s="41" t="s">
         <v>26</v>
       </c>
-      <c r="B20" s="22"/>
-      <c r="C20" s="36" t="s">
+      <c r="B20" s="29"/>
+      <c r="C20" s="30" t="s">
         <v>104</v>
       </c>
-      <c r="D20" s="30"/>
-      <c r="E20" s="30"/>
-      <c r="F20" s="30"/>
-      <c r="G20" s="22"/>
+      <c r="D20" s="28"/>
+      <c r="E20" s="28"/>
+      <c r="F20" s="28"/>
+      <c r="G20" s="29"/>
     </row>
     <row r="22" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="23" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -6634,25 +6634,12 @@
     <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="38">
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:G1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:E2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="C4:G4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C5:G5"/>
-    <mergeCell ref="A6:B7"/>
-    <mergeCell ref="D6:G6"/>
-    <mergeCell ref="D7:G7"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C20:G20"/>
+    <mergeCell ref="A17:B19"/>
+    <mergeCell ref="D17:G17"/>
+    <mergeCell ref="D18:G18"/>
+    <mergeCell ref="D19:G19"/>
     <mergeCell ref="A8:B8"/>
     <mergeCell ref="C8:G8"/>
     <mergeCell ref="A9:B9"/>
@@ -6664,14 +6651,27 @@
     <mergeCell ref="F11:G11"/>
     <mergeCell ref="D12:E12"/>
     <mergeCell ref="F12:G12"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C20:G20"/>
-    <mergeCell ref="A17:B19"/>
-    <mergeCell ref="D17:G17"/>
-    <mergeCell ref="D18:G18"/>
-    <mergeCell ref="D19:G19"/>
     <mergeCell ref="D16:E16"/>
     <mergeCell ref="F16:G16"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:G4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C5:G5"/>
+    <mergeCell ref="A6:B7"/>
+    <mergeCell ref="D6:G6"/>
+    <mergeCell ref="D7:G7"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:G1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:E2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="F15:G15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -6692,28 +6692,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="21" t="s">
+      <c r="B1" s="29"/>
+      <c r="C1" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="22"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="29"/>
     </row>
     <row r="2" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="22"/>
-      <c r="C2" s="38" t="s">
+      <c r="B2" s="29"/>
+      <c r="C2" s="56" t="s">
         <v>240</v>
       </c>
-      <c r="D2" s="30"/>
-      <c r="E2" s="22"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="29"/>
       <c r="F2" s="1" t="s">
         <v>4</v>
       </c>
@@ -6722,274 +6722,274 @@
       </c>
     </row>
     <row r="3" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A3" s="21" t="s">
+      <c r="A3" s="32" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="22"/>
-      <c r="C3" s="31" t="s">
+      <c r="B3" s="29"/>
+      <c r="C3" s="27" t="s">
         <v>28</v>
       </c>
-      <c r="D3" s="30"/>
-      <c r="E3" s="30"/>
-      <c r="F3" s="30"/>
-      <c r="G3" s="22"/>
+      <c r="D3" s="28"/>
+      <c r="E3" s="28"/>
+      <c r="F3" s="28"/>
+      <c r="G3" s="29"/>
     </row>
     <row r="4" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A4" s="21" t="s">
+      <c r="A4" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="22"/>
-      <c r="C4" s="32">
+      <c r="B4" s="29"/>
+      <c r="C4" s="42">
         <v>45789</v>
       </c>
-      <c r="D4" s="30"/>
-      <c r="E4" s="30"/>
-      <c r="F4" s="30"/>
-      <c r="G4" s="22"/>
+      <c r="D4" s="28"/>
+      <c r="E4" s="28"/>
+      <c r="F4" s="28"/>
+      <c r="G4" s="29"/>
     </row>
     <row r="5" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A5" s="21" t="s">
+      <c r="A5" s="32" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="22"/>
-      <c r="C5" s="31" t="s">
+      <c r="B5" s="29"/>
+      <c r="C5" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="D5" s="30"/>
-      <c r="E5" s="30"/>
-      <c r="F5" s="30"/>
-      <c r="G5" s="22"/>
+      <c r="D5" s="28"/>
+      <c r="E5" s="28"/>
+      <c r="F5" s="28"/>
+      <c r="G5" s="29"/>
     </row>
     <row r="6" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A6" s="23" t="s">
+      <c r="A6" s="35" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="24"/>
+      <c r="B6" s="36"/>
       <c r="C6" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D6" s="38" t="s">
+      <c r="D6" s="56" t="s">
         <v>131</v>
       </c>
-      <c r="E6" s="30"/>
-      <c r="F6" s="30"/>
-      <c r="G6" s="22"/>
+      <c r="E6" s="28"/>
+      <c r="F6" s="28"/>
+      <c r="G6" s="29"/>
     </row>
     <row r="7" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A7" s="25"/>
-      <c r="B7" s="26"/>
+      <c r="A7" s="39"/>
+      <c r="B7" s="40"/>
       <c r="C7" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D7" s="31"/>
-      <c r="E7" s="30"/>
-      <c r="F7" s="30"/>
-      <c r="G7" s="22"/>
+      <c r="D7" s="27"/>
+      <c r="E7" s="28"/>
+      <c r="F7" s="28"/>
+      <c r="G7" s="29"/>
     </row>
     <row r="8" spans="1:7" ht="60.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="27" t="s">
+      <c r="A8" s="41" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="22"/>
-      <c r="C8" s="35" t="s">
+      <c r="B8" s="29"/>
+      <c r="C8" s="31" t="s">
         <v>132</v>
       </c>
-      <c r="D8" s="30"/>
-      <c r="E8" s="30"/>
-      <c r="F8" s="30"/>
-      <c r="G8" s="22"/>
+      <c r="D8" s="28"/>
+      <c r="E8" s="28"/>
+      <c r="F8" s="28"/>
+      <c r="G8" s="29"/>
     </row>
     <row r="9" spans="1:7" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="27" t="s">
+      <c r="A9" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="22"/>
-      <c r="C9" s="35" t="s">
+      <c r="B9" s="29"/>
+      <c r="C9" s="31" t="s">
         <v>133</v>
       </c>
-      <c r="D9" s="30"/>
-      <c r="E9" s="30"/>
-      <c r="F9" s="30"/>
-      <c r="G9" s="22"/>
+      <c r="D9" s="28"/>
+      <c r="E9" s="28"/>
+      <c r="F9" s="28"/>
+      <c r="G9" s="29"/>
     </row>
     <row r="10" spans="1:7" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="41" t="s">
+      <c r="A10" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="B10" s="42"/>
+      <c r="B10" s="47"/>
       <c r="C10" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D10" s="66" t="s">
+      <c r="D10" s="69" t="s">
         <v>18</v>
       </c>
-      <c r="E10" s="67"/>
-      <c r="F10" s="66" t="s">
+      <c r="E10" s="70"/>
+      <c r="F10" s="69" t="s">
         <v>18</v>
       </c>
-      <c r="G10" s="67"/>
+      <c r="G10" s="70"/>
     </row>
     <row r="11" spans="1:7" ht="54.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="43"/>
-      <c r="B11" s="44"/>
-      <c r="C11" s="71">
+      <c r="A11" s="48"/>
+      <c r="B11" s="49"/>
+      <c r="C11" s="21">
         <v>1</v>
       </c>
-      <c r="D11" s="69" t="s">
+      <c r="D11" s="67" t="s">
         <v>241</v>
       </c>
-      <c r="E11" s="70"/>
-      <c r="F11" s="69" t="s">
+      <c r="E11" s="68"/>
+      <c r="F11" s="67" t="s">
         <v>242</v>
       </c>
-      <c r="G11" s="70"/>
+      <c r="G11" s="68"/>
     </row>
     <row r="12" spans="1:7" ht="54.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="43"/>
-      <c r="B12" s="44"/>
-      <c r="C12" s="71">
+      <c r="A12" s="48"/>
+      <c r="B12" s="49"/>
+      <c r="C12" s="21">
         <v>2</v>
       </c>
-      <c r="D12" s="70"/>
-      <c r="E12" s="70"/>
-      <c r="F12" s="69" t="s">
+      <c r="D12" s="68"/>
+      <c r="E12" s="68"/>
+      <c r="F12" s="67" t="s">
         <v>243</v>
       </c>
-      <c r="G12" s="70"/>
+      <c r="G12" s="68"/>
     </row>
     <row r="13" spans="1:7" ht="54.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="43"/>
-      <c r="B13" s="44"/>
-      <c r="C13" s="71">
+      <c r="A13" s="48"/>
+      <c r="B13" s="49"/>
+      <c r="C13" s="21">
         <v>3</v>
       </c>
-      <c r="D13" s="69" t="s">
+      <c r="D13" s="67" t="s">
         <v>244</v>
       </c>
-      <c r="E13" s="70"/>
-      <c r="F13" s="69" t="s">
+      <c r="E13" s="68"/>
+      <c r="F13" s="67" t="s">
         <v>245</v>
       </c>
-      <c r="G13" s="70"/>
+      <c r="G13" s="68"/>
     </row>
     <row r="14" spans="1:7" ht="54.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="43"/>
-      <c r="B14" s="44"/>
-      <c r="C14" s="71">
+      <c r="A14" s="48"/>
+      <c r="B14" s="49"/>
+      <c r="C14" s="21">
         <v>4</v>
       </c>
-      <c r="D14" s="69" t="s">
+      <c r="D14" s="67" t="s">
         <v>246</v>
       </c>
-      <c r="E14" s="70"/>
-      <c r="F14" s="70"/>
-      <c r="G14" s="70"/>
+      <c r="E14" s="68"/>
+      <c r="F14" s="68"/>
+      <c r="G14" s="68"/>
     </row>
     <row r="15" spans="1:7" ht="54.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="43"/>
-      <c r="B15" s="44"/>
-      <c r="C15" s="71">
+      <c r="A15" s="48"/>
+      <c r="B15" s="49"/>
+      <c r="C15" s="21">
         <v>5</v>
       </c>
-      <c r="D15" s="70"/>
-      <c r="E15" s="70"/>
-      <c r="F15" s="69" t="s">
+      <c r="D15" s="68"/>
+      <c r="E15" s="68"/>
+      <c r="F15" s="67" t="s">
         <v>247</v>
       </c>
-      <c r="G15" s="70"/>
+      <c r="G15" s="68"/>
     </row>
     <row r="16" spans="1:7" ht="54.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="43"/>
-      <c r="B16" s="44"/>
-      <c r="C16" s="71">
+      <c r="A16" s="48"/>
+      <c r="B16" s="49"/>
+      <c r="C16" s="21">
         <v>6</v>
       </c>
-      <c r="D16" s="70"/>
-      <c r="E16" s="70"/>
-      <c r="F16" s="69" t="s">
+      <c r="D16" s="68"/>
+      <c r="E16" s="68"/>
+      <c r="F16" s="67" t="s">
         <v>248</v>
       </c>
-      <c r="G16" s="70"/>
+      <c r="G16" s="68"/>
     </row>
     <row r="17" spans="1:7" ht="54.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="43"/>
-      <c r="B17" s="44"/>
-      <c r="C17" s="71">
+      <c r="A17" s="48"/>
+      <c r="B17" s="49"/>
+      <c r="C17" s="21">
         <v>7</v>
       </c>
-      <c r="D17" s="70"/>
-      <c r="E17" s="70"/>
-      <c r="F17" s="69" t="s">
+      <c r="D17" s="68"/>
+      <c r="E17" s="68"/>
+      <c r="F17" s="67" t="s">
         <v>249</v>
       </c>
-      <c r="G17" s="70"/>
+      <c r="G17" s="68"/>
     </row>
     <row r="18" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="23" t="s">
+      <c r="A18" s="35" t="s">
         <v>19</v>
       </c>
-      <c r="B18" s="24"/>
+      <c r="B18" s="36"/>
       <c r="C18" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D18" s="21" t="s">
+      <c r="D18" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="E18" s="30"/>
-      <c r="F18" s="30"/>
-      <c r="G18" s="22"/>
+      <c r="E18" s="28"/>
+      <c r="F18" s="28"/>
+      <c r="G18" s="29"/>
     </row>
     <row r="19" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="28"/>
-      <c r="B19" s="29"/>
+      <c r="A19" s="37"/>
+      <c r="B19" s="38"/>
       <c r="C19" s="16" t="s">
         <v>126</v>
       </c>
-      <c r="D19" s="35" t="s">
+      <c r="D19" s="31" t="s">
         <v>124</v>
       </c>
-      <c r="E19" s="30"/>
-      <c r="F19" s="30"/>
-      <c r="G19" s="22"/>
+      <c r="E19" s="28"/>
+      <c r="F19" s="28"/>
+      <c r="G19" s="29"/>
     </row>
     <row r="20" spans="1:7" ht="46.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="28"/>
-      <c r="B20" s="29"/>
+      <c r="A20" s="37"/>
+      <c r="B20" s="38"/>
       <c r="C20" s="17" t="s">
         <v>99</v>
       </c>
-      <c r="D20" s="35" t="s">
+      <c r="D20" s="31" t="s">
         <v>135</v>
       </c>
-      <c r="E20" s="30"/>
-      <c r="F20" s="30"/>
-      <c r="G20" s="22"/>
+      <c r="E20" s="28"/>
+      <c r="F20" s="28"/>
+      <c r="G20" s="29"/>
     </row>
     <row r="21" spans="1:7" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="25"/>
-      <c r="B21" s="26"/>
+      <c r="A21" s="39"/>
+      <c r="B21" s="40"/>
       <c r="C21" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="D21" s="35" t="s">
+      <c r="D21" s="31" t="s">
         <v>136</v>
       </c>
-      <c r="E21" s="30"/>
-      <c r="F21" s="30"/>
-      <c r="G21" s="22"/>
+      <c r="E21" s="28"/>
+      <c r="F21" s="28"/>
+      <c r="G21" s="29"/>
     </row>
     <row r="22" spans="1:7" ht="46.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="27" t="s">
+      <c r="A22" s="41" t="s">
         <v>26</v>
       </c>
-      <c r="B22" s="22"/>
-      <c r="C22" s="35" t="s">
+      <c r="B22" s="29"/>
+      <c r="C22" s="31" t="s">
         <v>134</v>
       </c>
-      <c r="D22" s="30"/>
-      <c r="E22" s="30"/>
-      <c r="F22" s="30"/>
-      <c r="G22" s="22"/>
+      <c r="D22" s="28"/>
+      <c r="E22" s="28"/>
+      <c r="F22" s="28"/>
+      <c r="G22" s="29"/>
     </row>
     <row r="24" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="25" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -7688,25 +7688,13 @@
     <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="41">
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:G1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:E2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="C4:G4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C5:G5"/>
-    <mergeCell ref="A6:B7"/>
-    <mergeCell ref="D6:G6"/>
-    <mergeCell ref="D7:G7"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:G22"/>
+    <mergeCell ref="A18:B21"/>
+    <mergeCell ref="D18:G18"/>
+    <mergeCell ref="D19:G19"/>
+    <mergeCell ref="D20:G20"/>
+    <mergeCell ref="D21:G21"/>
     <mergeCell ref="A8:B8"/>
     <mergeCell ref="C8:G8"/>
     <mergeCell ref="A9:B9"/>
@@ -7718,17 +7706,29 @@
     <mergeCell ref="F11:G11"/>
     <mergeCell ref="D12:E12"/>
     <mergeCell ref="F12:G12"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:G22"/>
-    <mergeCell ref="A18:B21"/>
-    <mergeCell ref="D18:G18"/>
-    <mergeCell ref="D19:G19"/>
-    <mergeCell ref="D20:G20"/>
-    <mergeCell ref="D21:G21"/>
     <mergeCell ref="D16:E16"/>
     <mergeCell ref="F16:G16"/>
     <mergeCell ref="D17:E17"/>
     <mergeCell ref="F17:G17"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:G4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C5:G5"/>
+    <mergeCell ref="A6:B7"/>
+    <mergeCell ref="D6:G6"/>
+    <mergeCell ref="D7:G7"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:G1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:E2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="F15:G15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -7749,28 +7749,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="21" t="s">
+      <c r="B1" s="29"/>
+      <c r="C1" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="22"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="29"/>
     </row>
     <row r="2" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="22"/>
-      <c r="C2" s="31" t="s">
+      <c r="B2" s="29"/>
+      <c r="C2" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="D2" s="30"/>
-      <c r="E2" s="22"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="29"/>
       <c r="F2" s="1" t="s">
         <v>4</v>
       </c>
@@ -7779,289 +7779,289 @@
       </c>
     </row>
     <row r="3" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A3" s="21" t="s">
+      <c r="A3" s="32" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="22"/>
-      <c r="C3" s="31" t="s">
+      <c r="B3" s="29"/>
+      <c r="C3" s="27" t="s">
         <v>28</v>
       </c>
-      <c r="D3" s="30"/>
-      <c r="E3" s="30"/>
-      <c r="F3" s="30"/>
-      <c r="G3" s="22"/>
+      <c r="D3" s="28"/>
+      <c r="E3" s="28"/>
+      <c r="F3" s="28"/>
+      <c r="G3" s="29"/>
     </row>
     <row r="4" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A4" s="21" t="s">
+      <c r="A4" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="22"/>
-      <c r="C4" s="32">
+      <c r="B4" s="29"/>
+      <c r="C4" s="42">
         <v>45789</v>
       </c>
-      <c r="D4" s="30"/>
-      <c r="E4" s="30"/>
-      <c r="F4" s="30"/>
-      <c r="G4" s="22"/>
+      <c r="D4" s="28"/>
+      <c r="E4" s="28"/>
+      <c r="F4" s="28"/>
+      <c r="G4" s="29"/>
     </row>
     <row r="5" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A5" s="21" t="s">
+      <c r="A5" s="32" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="22"/>
-      <c r="C5" s="31" t="s">
+      <c r="B5" s="29"/>
+      <c r="C5" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="D5" s="30"/>
-      <c r="E5" s="30"/>
-      <c r="F5" s="30"/>
-      <c r="G5" s="22"/>
+      <c r="D5" s="28"/>
+      <c r="E5" s="28"/>
+      <c r="F5" s="28"/>
+      <c r="G5" s="29"/>
     </row>
     <row r="6" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A6" s="23" t="s">
+      <c r="A6" s="35" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="24"/>
+      <c r="B6" s="36"/>
       <c r="C6" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D6" s="31" t="s">
+      <c r="D6" s="27" t="s">
         <v>30</v>
       </c>
-      <c r="E6" s="30"/>
-      <c r="F6" s="30"/>
-      <c r="G6" s="22"/>
+      <c r="E6" s="28"/>
+      <c r="F6" s="28"/>
+      <c r="G6" s="29"/>
     </row>
     <row r="7" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A7" s="25"/>
-      <c r="B7" s="26"/>
+      <c r="A7" s="39"/>
+      <c r="B7" s="40"/>
       <c r="C7" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D7" s="31"/>
-      <c r="E7" s="30"/>
-      <c r="F7" s="30"/>
-      <c r="G7" s="22"/>
+      <c r="D7" s="27"/>
+      <c r="E7" s="28"/>
+      <c r="F7" s="28"/>
+      <c r="G7" s="29"/>
     </row>
     <row r="8" spans="1:7" ht="57.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="27" t="s">
+      <c r="A8" s="41" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="22"/>
-      <c r="C8" s="35" t="s">
+      <c r="B8" s="29"/>
+      <c r="C8" s="31" t="s">
         <v>32</v>
       </c>
-      <c r="D8" s="30"/>
-      <c r="E8" s="30"/>
-      <c r="F8" s="30"/>
-      <c r="G8" s="22"/>
+      <c r="D8" s="28"/>
+      <c r="E8" s="28"/>
+      <c r="F8" s="28"/>
+      <c r="G8" s="29"/>
     </row>
     <row r="9" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="27" t="s">
+      <c r="A9" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="22"/>
-      <c r="C9" s="35" t="s">
+      <c r="B9" s="29"/>
+      <c r="C9" s="31" t="s">
         <v>33</v>
       </c>
-      <c r="D9" s="30"/>
-      <c r="E9" s="30"/>
-      <c r="F9" s="30"/>
-      <c r="G9" s="22"/>
+      <c r="D9" s="28"/>
+      <c r="E9" s="28"/>
+      <c r="F9" s="28"/>
+      <c r="G9" s="29"/>
     </row>
     <row r="10" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A10" s="41" t="s">
+      <c r="A10" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="B10" s="42"/>
+      <c r="B10" s="47"/>
       <c r="C10" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D10" s="56" t="s">
+      <c r="D10" s="50" t="s">
         <v>137</v>
       </c>
-      <c r="E10" s="49"/>
-      <c r="F10" s="56" t="s">
+      <c r="E10" s="34"/>
+      <c r="F10" s="50" t="s">
         <v>138</v>
       </c>
-      <c r="G10" s="49"/>
+      <c r="G10" s="34"/>
     </row>
     <row r="11" spans="1:7" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="43"/>
-      <c r="B11" s="44"/>
+      <c r="A11" s="48"/>
+      <c r="B11" s="49"/>
       <c r="C11" s="13">
         <v>1</v>
       </c>
-      <c r="D11" s="54" t="s">
+      <c r="D11" s="24" t="s">
         <v>146</v>
       </c>
-      <c r="E11" s="55"/>
-      <c r="F11" s="54" t="s">
+      <c r="E11" s="45"/>
+      <c r="F11" s="24" t="s">
         <v>147</v>
       </c>
-      <c r="G11" s="55"/>
+      <c r="G11" s="45"/>
     </row>
     <row r="12" spans="1:7" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="43"/>
-      <c r="B12" s="44"/>
+      <c r="A12" s="48"/>
+      <c r="B12" s="49"/>
       <c r="C12" s="13">
         <v>2</v>
       </c>
-      <c r="D12" s="54" t="s">
+      <c r="D12" s="24" t="s">
         <v>148</v>
       </c>
-      <c r="E12" s="55"/>
-      <c r="F12" s="54" t="s">
+      <c r="E12" s="45"/>
+      <c r="F12" s="24" t="s">
         <v>149</v>
       </c>
-      <c r="G12" s="55"/>
+      <c r="G12" s="45"/>
     </row>
     <row r="13" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="43"/>
-      <c r="B13" s="44"/>
+      <c r="A13" s="48"/>
+      <c r="B13" s="49"/>
       <c r="C13" s="13">
         <v>3</v>
       </c>
-      <c r="D13" s="54" t="s">
+      <c r="D13" s="24" t="s">
         <v>150</v>
       </c>
-      <c r="E13" s="55"/>
-      <c r="F13" s="54"/>
-      <c r="G13" s="55"/>
+      <c r="E13" s="45"/>
+      <c r="F13" s="24"/>
+      <c r="G13" s="45"/>
     </row>
     <row r="14" spans="1:7" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="43"/>
-      <c r="B14" s="44"/>
+      <c r="A14" s="48"/>
+      <c r="B14" s="49"/>
       <c r="C14" s="13">
         <v>4</v>
       </c>
-      <c r="D14" s="54" t="s">
+      <c r="D14" s="24" t="s">
         <v>151</v>
       </c>
-      <c r="E14" s="55"/>
-      <c r="F14" s="54" t="s">
+      <c r="E14" s="45"/>
+      <c r="F14" s="24" t="s">
         <v>152</v>
       </c>
-      <c r="G14" s="55"/>
+      <c r="G14" s="45"/>
     </row>
     <row r="15" spans="1:7" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="43"/>
-      <c r="B15" s="44"/>
+      <c r="A15" s="48"/>
+      <c r="B15" s="49"/>
       <c r="C15" s="13">
         <v>5</v>
       </c>
-      <c r="D15" s="54"/>
-      <c r="E15" s="55"/>
-      <c r="F15" s="54" t="s">
+      <c r="D15" s="24"/>
+      <c r="E15" s="45"/>
+      <c r="F15" s="24" t="s">
         <v>153</v>
       </c>
-      <c r="G15" s="55"/>
+      <c r="G15" s="45"/>
     </row>
     <row r="16" spans="1:7" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="43"/>
-      <c r="B16" s="44"/>
+      <c r="A16" s="48"/>
+      <c r="B16" s="49"/>
       <c r="C16" s="13">
         <v>6</v>
       </c>
-      <c r="D16" s="54"/>
-      <c r="E16" s="55"/>
-      <c r="F16" s="54" t="s">
+      <c r="D16" s="24"/>
+      <c r="E16" s="45"/>
+      <c r="F16" s="24" t="s">
         <v>155</v>
       </c>
-      <c r="G16" s="55"/>
+      <c r="G16" s="45"/>
     </row>
     <row r="17" spans="1:7" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="43"/>
-      <c r="B17" s="44"/>
+      <c r="A17" s="48"/>
+      <c r="B17" s="49"/>
       <c r="C17" s="13">
         <v>7</v>
       </c>
-      <c r="D17" s="54"/>
-      <c r="E17" s="55"/>
-      <c r="F17" s="54" t="s">
+      <c r="D17" s="24"/>
+      <c r="E17" s="45"/>
+      <c r="F17" s="24" t="s">
         <v>154</v>
       </c>
-      <c r="G17" s="55"/>
+      <c r="G17" s="45"/>
     </row>
     <row r="18" spans="1:7" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="39" t="s">
+      <c r="A18" s="51" t="s">
         <v>19</v>
       </c>
-      <c r="B18" s="39"/>
+      <c r="B18" s="51"/>
       <c r="C18" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D18" s="21" t="s">
+      <c r="D18" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="E18" s="30"/>
-      <c r="F18" s="30"/>
-      <c r="G18" s="22"/>
+      <c r="E18" s="28"/>
+      <c r="F18" s="28"/>
+      <c r="G18" s="29"/>
     </row>
     <row r="19" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="40"/>
-      <c r="B19" s="40"/>
+      <c r="A19" s="52"/>
+      <c r="B19" s="52"/>
       <c r="C19" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="D19" s="35" t="s">
+      <c r="D19" s="31" t="s">
         <v>35</v>
       </c>
-      <c r="E19" s="30"/>
-      <c r="F19" s="30"/>
-      <c r="G19" s="22"/>
+      <c r="E19" s="28"/>
+      <c r="F19" s="28"/>
+      <c r="G19" s="29"/>
     </row>
     <row r="20" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="40"/>
-      <c r="B20" s="40"/>
+      <c r="A20" s="52"/>
+      <c r="B20" s="52"/>
       <c r="C20" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="D20" s="35" t="s">
+      <c r="D20" s="31" t="s">
         <v>36</v>
       </c>
-      <c r="E20" s="30"/>
-      <c r="F20" s="30"/>
-      <c r="G20" s="22"/>
+      <c r="E20" s="28"/>
+      <c r="F20" s="28"/>
+      <c r="G20" s="29"/>
     </row>
     <row r="21" spans="1:7" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="40"/>
-      <c r="B21" s="40"/>
+      <c r="A21" s="52"/>
+      <c r="B21" s="52"/>
       <c r="C21" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="D21" s="35" t="s">
+      <c r="D21" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="E21" s="30"/>
-      <c r="F21" s="30"/>
-      <c r="G21" s="22"/>
+      <c r="E21" s="28"/>
+      <c r="F21" s="28"/>
+      <c r="G21" s="29"/>
     </row>
     <row r="22" spans="1:7" ht="49.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="40"/>
-      <c r="B22" s="40"/>
+      <c r="A22" s="52"/>
+      <c r="B22" s="52"/>
       <c r="C22" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="D22" s="35" t="s">
+      <c r="D22" s="31" t="s">
         <v>38</v>
       </c>
-      <c r="E22" s="30"/>
-      <c r="F22" s="30"/>
-      <c r="G22" s="22"/>
+      <c r="E22" s="28"/>
+      <c r="F22" s="28"/>
+      <c r="G22" s="29"/>
     </row>
     <row r="23" spans="1:7" ht="48" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="27" t="s">
+      <c r="A23" s="41" t="s">
         <v>26</v>
       </c>
-      <c r="B23" s="22"/>
-      <c r="C23" s="35" t="s">
+      <c r="B23" s="29"/>
+      <c r="C23" s="31" t="s">
         <v>34</v>
       </c>
-      <c r="D23" s="30"/>
-      <c r="E23" s="30"/>
-      <c r="F23" s="30"/>
-      <c r="G23" s="22"/>
+      <c r="D23" s="28"/>
+      <c r="E23" s="28"/>
+      <c r="F23" s="28"/>
+      <c r="G23" s="29"/>
     </row>
     <row r="24" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="25" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -8755,34 +8755,6 @@
     <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="42">
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A10:B17"/>
-    <mergeCell ref="D20:G20"/>
-    <mergeCell ref="D21:G21"/>
-    <mergeCell ref="D18:G18"/>
-    <mergeCell ref="D19:G19"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="C4:G4"/>
-    <mergeCell ref="C5:G5"/>
-    <mergeCell ref="D6:G6"/>
-    <mergeCell ref="D7:G7"/>
-    <mergeCell ref="C8:G8"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:G1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:E2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="C3:G3"/>
     <mergeCell ref="A23:B23"/>
     <mergeCell ref="C23:G23"/>
     <mergeCell ref="A6:B7"/>
@@ -8797,6 +8769,34 @@
     <mergeCell ref="D12:E12"/>
     <mergeCell ref="F12:G12"/>
     <mergeCell ref="D13:E13"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:G1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:E2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A10:B17"/>
+    <mergeCell ref="D20:G20"/>
+    <mergeCell ref="D21:G21"/>
+    <mergeCell ref="D18:G18"/>
+    <mergeCell ref="D19:G19"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="C4:G4"/>
+    <mergeCell ref="C5:G5"/>
+    <mergeCell ref="D6:G6"/>
+    <mergeCell ref="D7:G7"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="F15:G15"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -8815,28 +8815,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="21" t="s">
+      <c r="B1" s="29"/>
+      <c r="C1" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="22"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="29"/>
     </row>
     <row r="2" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="22"/>
-      <c r="C2" s="38" t="s">
+      <c r="B2" s="29"/>
+      <c r="C2" s="56" t="s">
         <v>44</v>
       </c>
-      <c r="D2" s="30"/>
-      <c r="E2" s="22"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="29"/>
       <c r="F2" s="1" t="s">
         <v>4</v>
       </c>
@@ -8845,265 +8845,265 @@
       </c>
     </row>
     <row r="3" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A3" s="21" t="s">
+      <c r="A3" s="32" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="22"/>
-      <c r="C3" s="31" t="s">
+      <c r="B3" s="29"/>
+      <c r="C3" s="27" t="s">
         <v>28</v>
       </c>
-      <c r="D3" s="30"/>
-      <c r="E3" s="30"/>
-      <c r="F3" s="30"/>
-      <c r="G3" s="22"/>
+      <c r="D3" s="28"/>
+      <c r="E3" s="28"/>
+      <c r="F3" s="28"/>
+      <c r="G3" s="29"/>
     </row>
     <row r="4" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A4" s="21" t="s">
+      <c r="A4" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="22"/>
-      <c r="C4" s="32">
+      <c r="B4" s="29"/>
+      <c r="C4" s="42">
         <v>45789</v>
       </c>
-      <c r="D4" s="30"/>
-      <c r="E4" s="30"/>
-      <c r="F4" s="30"/>
-      <c r="G4" s="22"/>
+      <c r="D4" s="28"/>
+      <c r="E4" s="28"/>
+      <c r="F4" s="28"/>
+      <c r="G4" s="29"/>
     </row>
     <row r="5" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A5" s="21" t="s">
+      <c r="A5" s="32" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="22"/>
-      <c r="C5" s="31" t="s">
+      <c r="B5" s="29"/>
+      <c r="C5" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="D5" s="30"/>
-      <c r="E5" s="30"/>
-      <c r="F5" s="30"/>
-      <c r="G5" s="22"/>
+      <c r="D5" s="28"/>
+      <c r="E5" s="28"/>
+      <c r="F5" s="28"/>
+      <c r="G5" s="29"/>
     </row>
     <row r="6" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="23" t="s">
+      <c r="A6" s="35" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="24"/>
+      <c r="B6" s="36"/>
       <c r="C6" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D6" s="31" t="s">
+      <c r="D6" s="27" t="s">
         <v>30</v>
       </c>
-      <c r="E6" s="30"/>
-      <c r="F6" s="30"/>
-      <c r="G6" s="22"/>
+      <c r="E6" s="28"/>
+      <c r="F6" s="28"/>
+      <c r="G6" s="29"/>
     </row>
     <row r="7" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="25"/>
-      <c r="B7" s="26"/>
+      <c r="A7" s="39"/>
+      <c r="B7" s="40"/>
       <c r="C7" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D7" s="31"/>
-      <c r="E7" s="30"/>
-      <c r="F7" s="30"/>
-      <c r="G7" s="22"/>
+      <c r="D7" s="27"/>
+      <c r="E7" s="28"/>
+      <c r="F7" s="28"/>
+      <c r="G7" s="29"/>
     </row>
     <row r="8" spans="1:7" ht="46.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="27" t="s">
+      <c r="A8" s="41" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="22"/>
-      <c r="C8" s="35" t="s">
+      <c r="B8" s="29"/>
+      <c r="C8" s="31" t="s">
         <v>51</v>
       </c>
-      <c r="D8" s="30"/>
-      <c r="E8" s="30"/>
-      <c r="F8" s="30"/>
-      <c r="G8" s="22"/>
+      <c r="D8" s="28"/>
+      <c r="E8" s="28"/>
+      <c r="F8" s="28"/>
+      <c r="G8" s="29"/>
     </row>
     <row r="9" spans="1:7" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="27" t="s">
+      <c r="A9" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="22"/>
-      <c r="C9" s="35" t="s">
+      <c r="B9" s="29"/>
+      <c r="C9" s="31" t="s">
         <v>45</v>
       </c>
-      <c r="D9" s="30"/>
-      <c r="E9" s="30"/>
-      <c r="F9" s="30"/>
-      <c r="G9" s="22"/>
+      <c r="D9" s="28"/>
+      <c r="E9" s="28"/>
+      <c r="F9" s="28"/>
+      <c r="G9" s="29"/>
     </row>
     <row r="10" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A10" s="41" t="s">
+      <c r="A10" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="B10" s="42"/>
+      <c r="B10" s="47"/>
       <c r="C10" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D10" s="56" t="s">
+      <c r="D10" s="50" t="s">
         <v>18</v>
       </c>
-      <c r="E10" s="57"/>
-      <c r="F10" s="56" t="s">
+      <c r="E10" s="55"/>
+      <c r="F10" s="50" t="s">
         <v>18</v>
       </c>
-      <c r="G10" s="57"/>
+      <c r="G10" s="55"/>
     </row>
     <row r="11" spans="1:7" ht="61.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="43"/>
-      <c r="B11" s="44"/>
+      <c r="A11" s="48"/>
+      <c r="B11" s="49"/>
       <c r="C11" s="13">
         <v>1</v>
       </c>
-      <c r="D11" s="58" t="s">
+      <c r="D11" s="53" t="s">
         <v>47</v>
       </c>
-      <c r="E11" s="59"/>
-      <c r="F11" s="60" t="s">
+      <c r="E11" s="54"/>
+      <c r="F11" s="57" t="s">
         <v>156</v>
       </c>
-      <c r="G11" s="61"/>
+      <c r="G11" s="58"/>
     </row>
     <row r="12" spans="1:7" ht="42.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="43"/>
-      <c r="B12" s="44"/>
+      <c r="A12" s="48"/>
+      <c r="B12" s="49"/>
       <c r="C12" s="13">
         <v>2</v>
       </c>
-      <c r="D12" s="58" t="s">
+      <c r="D12" s="53" t="s">
         <v>48</v>
       </c>
-      <c r="E12" s="59"/>
-      <c r="F12" s="60" t="s">
+      <c r="E12" s="54"/>
+      <c r="F12" s="57" t="s">
         <v>157</v>
       </c>
-      <c r="G12" s="61"/>
+      <c r="G12" s="58"/>
     </row>
     <row r="13" spans="1:7" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="43"/>
-      <c r="B13" s="44"/>
+      <c r="A13" s="48"/>
+      <c r="B13" s="49"/>
       <c r="C13" s="13">
         <v>3</v>
       </c>
-      <c r="D13" s="58"/>
-      <c r="E13" s="59"/>
-      <c r="F13" s="60" t="s">
+      <c r="D13" s="53"/>
+      <c r="E13" s="54"/>
+      <c r="F13" s="57" t="s">
         <v>158</v>
       </c>
-      <c r="G13" s="61"/>
+      <c r="G13" s="58"/>
     </row>
     <row r="14" spans="1:7" ht="58.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="43"/>
-      <c r="B14" s="44"/>
+      <c r="A14" s="48"/>
+      <c r="B14" s="49"/>
       <c r="C14" s="13">
         <v>4</v>
       </c>
-      <c r="D14" s="58" t="s">
+      <c r="D14" s="53" t="s">
         <v>49</v>
       </c>
-      <c r="E14" s="59"/>
-      <c r="F14" s="60" t="s">
+      <c r="E14" s="54"/>
+      <c r="F14" s="57" t="s">
         <v>159</v>
       </c>
-      <c r="G14" s="61"/>
+      <c r="G14" s="58"/>
     </row>
     <row r="15" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="43"/>
-      <c r="B15" s="44"/>
+      <c r="A15" s="48"/>
+      <c r="B15" s="49"/>
       <c r="C15" s="13">
         <v>5</v>
       </c>
-      <c r="D15" s="58" t="s">
+      <c r="D15" s="53" t="s">
         <v>50</v>
       </c>
-      <c r="E15" s="59"/>
-      <c r="F15" s="60" t="s">
+      <c r="E15" s="54"/>
+      <c r="F15" s="57" t="s">
         <v>160</v>
       </c>
-      <c r="G15" s="61"/>
+      <c r="G15" s="58"/>
     </row>
     <row r="16" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="43"/>
-      <c r="B16" s="44"/>
+      <c r="A16" s="48"/>
+      <c r="B16" s="49"/>
       <c r="C16" s="13">
         <v>6</v>
       </c>
-      <c r="D16" s="58"/>
-      <c r="E16" s="59"/>
-      <c r="F16" s="52" t="s">
+      <c r="D16" s="53"/>
+      <c r="E16" s="54"/>
+      <c r="F16" s="22" t="s">
         <v>161</v>
       </c>
-      <c r="G16" s="53"/>
+      <c r="G16" s="23"/>
     </row>
     <row r="17" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="43"/>
-      <c r="B17" s="44"/>
+      <c r="A17" s="48"/>
+      <c r="B17" s="49"/>
       <c r="C17" s="13">
         <v>7</v>
       </c>
-      <c r="D17" s="54"/>
-      <c r="E17" s="55"/>
-      <c r="F17" s="52" t="s">
+      <c r="D17" s="24"/>
+      <c r="E17" s="45"/>
+      <c r="F17" s="22" t="s">
         <v>162</v>
       </c>
-      <c r="G17" s="53"/>
+      <c r="G17" s="23"/>
     </row>
     <row r="18" spans="1:7" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="23" t="s">
+      <c r="A18" s="35" t="s">
         <v>19</v>
       </c>
-      <c r="B18" s="24"/>
+      <c r="B18" s="36"/>
       <c r="C18" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D18" s="21" t="s">
+      <c r="D18" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="E18" s="30"/>
-      <c r="F18" s="30"/>
-      <c r="G18" s="22"/>
+      <c r="E18" s="28"/>
+      <c r="F18" s="28"/>
+      <c r="G18" s="29"/>
     </row>
     <row r="19" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="28"/>
-      <c r="B19" s="29"/>
+      <c r="A19" s="37"/>
+      <c r="B19" s="38"/>
       <c r="C19" s="7">
         <v>45298</v>
       </c>
-      <c r="D19" s="35" t="s">
+      <c r="D19" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="E19" s="30"/>
-      <c r="F19" s="30"/>
-      <c r="G19" s="22"/>
+      <c r="E19" s="28"/>
+      <c r="F19" s="28"/>
+      <c r="G19" s="29"/>
     </row>
     <row r="20" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="28"/>
-      <c r="B20" s="29"/>
+      <c r="A20" s="37"/>
+      <c r="B20" s="38"/>
       <c r="C20" s="7">
         <v>45329</v>
       </c>
-      <c r="D20" s="35" t="s">
+      <c r="D20" s="31" t="s">
         <v>53</v>
       </c>
-      <c r="E20" s="30"/>
-      <c r="F20" s="30"/>
-      <c r="G20" s="22"/>
+      <c r="E20" s="28"/>
+      <c r="F20" s="28"/>
+      <c r="G20" s="29"/>
     </row>
     <row r="21" spans="1:7" ht="59.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="27" t="s">
+      <c r="A21" s="41" t="s">
         <v>26</v>
       </c>
-      <c r="B21" s="22"/>
-      <c r="C21" s="35" t="s">
+      <c r="B21" s="29"/>
+      <c r="C21" s="31" t="s">
         <v>46</v>
       </c>
-      <c r="D21" s="30"/>
-      <c r="E21" s="30"/>
-      <c r="F21" s="30"/>
-      <c r="G21" s="22"/>
+      <c r="D21" s="28"/>
+      <c r="E21" s="28"/>
+      <c r="F21" s="28"/>
+      <c r="G21" s="29"/>
     </row>
     <row r="22" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="23" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -9800,31 +9800,6 @@
     <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="40">
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="D18:G18"/>
-    <mergeCell ref="D19:G19"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="C4:G4"/>
-    <mergeCell ref="C5:G5"/>
-    <mergeCell ref="D6:G6"/>
-    <mergeCell ref="D7:G7"/>
-    <mergeCell ref="C8:G8"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:G1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:E2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A6:B7"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="A9:B9"/>
     <mergeCell ref="A10:B17"/>
     <mergeCell ref="A18:B20"/>
     <mergeCell ref="D20:G20"/>
@@ -9840,6 +9815,31 @@
     <mergeCell ref="F16:G16"/>
     <mergeCell ref="F17:G17"/>
     <mergeCell ref="D13:E13"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A6:B7"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:G1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:E2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="C4:G4"/>
+    <mergeCell ref="C5:G5"/>
+    <mergeCell ref="D6:G6"/>
+    <mergeCell ref="D7:G7"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="D18:G18"/>
+    <mergeCell ref="D19:G19"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="D12:E12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -9859,28 +9859,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="21" t="s">
+      <c r="B1" s="29"/>
+      <c r="C1" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="22"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="29"/>
     </row>
     <row r="2" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="22"/>
-      <c r="C2" s="38" t="s">
+      <c r="B2" s="29"/>
+      <c r="C2" s="56" t="s">
         <v>54</v>
       </c>
-      <c r="D2" s="30"/>
-      <c r="E2" s="22"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="29"/>
       <c r="F2" s="1" t="s">
         <v>4</v>
       </c>
@@ -9889,183 +9889,183 @@
       </c>
     </row>
     <row r="3" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A3" s="21" t="s">
+      <c r="A3" s="32" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="22"/>
-      <c r="C3" s="31" t="s">
+      <c r="B3" s="29"/>
+      <c r="C3" s="27" t="s">
         <v>28</v>
       </c>
-      <c r="D3" s="30"/>
-      <c r="E3" s="30"/>
-      <c r="F3" s="30"/>
-      <c r="G3" s="22"/>
+      <c r="D3" s="28"/>
+      <c r="E3" s="28"/>
+      <c r="F3" s="28"/>
+      <c r="G3" s="29"/>
     </row>
     <row r="4" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A4" s="21" t="s">
+      <c r="A4" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="22"/>
-      <c r="C4" s="32">
+      <c r="B4" s="29"/>
+      <c r="C4" s="42">
         <v>45789</v>
       </c>
-      <c r="D4" s="30"/>
-      <c r="E4" s="30"/>
-      <c r="F4" s="30"/>
-      <c r="G4" s="22"/>
+      <c r="D4" s="28"/>
+      <c r="E4" s="28"/>
+      <c r="F4" s="28"/>
+      <c r="G4" s="29"/>
     </row>
     <row r="5" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A5" s="21" t="s">
+      <c r="A5" s="32" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="22"/>
-      <c r="C5" s="31" t="s">
+      <c r="B5" s="29"/>
+      <c r="C5" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="D5" s="30"/>
-      <c r="E5" s="30"/>
-      <c r="F5" s="30"/>
-      <c r="G5" s="22"/>
+      <c r="D5" s="28"/>
+      <c r="E5" s="28"/>
+      <c r="F5" s="28"/>
+      <c r="G5" s="29"/>
     </row>
     <row r="6" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A6" s="23" t="s">
+      <c r="A6" s="35" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="24"/>
+      <c r="B6" s="36"/>
       <c r="C6" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D6" s="38" t="s">
+      <c r="D6" s="56" t="s">
         <v>31</v>
       </c>
-      <c r="E6" s="30"/>
-      <c r="F6" s="30"/>
-      <c r="G6" s="22"/>
+      <c r="E6" s="28"/>
+      <c r="F6" s="28"/>
+      <c r="G6" s="29"/>
     </row>
     <row r="7" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A7" s="25"/>
-      <c r="B7" s="26"/>
+      <c r="A7" s="39"/>
+      <c r="B7" s="40"/>
       <c r="C7" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D7" s="31"/>
-      <c r="E7" s="30"/>
-      <c r="F7" s="30"/>
-      <c r="G7" s="22"/>
+      <c r="D7" s="27"/>
+      <c r="E7" s="28"/>
+      <c r="F7" s="28"/>
+      <c r="G7" s="29"/>
     </row>
     <row r="8" spans="1:7" ht="34.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="27" t="s">
+      <c r="A8" s="41" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="22"/>
-      <c r="C8" s="35" t="s">
+      <c r="B8" s="29"/>
+      <c r="C8" s="31" t="s">
         <v>55</v>
       </c>
-      <c r="D8" s="30"/>
-      <c r="E8" s="30"/>
-      <c r="F8" s="30"/>
-      <c r="G8" s="22"/>
+      <c r="D8" s="28"/>
+      <c r="E8" s="28"/>
+      <c r="F8" s="28"/>
+      <c r="G8" s="29"/>
     </row>
     <row r="9" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="27" t="s">
+      <c r="A9" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="22"/>
-      <c r="C9" s="35" t="s">
+      <c r="B9" s="29"/>
+      <c r="C9" s="31" t="s">
         <v>45</v>
       </c>
-      <c r="D9" s="30"/>
-      <c r="E9" s="30"/>
-      <c r="F9" s="30"/>
-      <c r="G9" s="22"/>
+      <c r="D9" s="28"/>
+      <c r="E9" s="28"/>
+      <c r="F9" s="28"/>
+      <c r="G9" s="29"/>
     </row>
     <row r="10" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A10" s="41" t="s">
+      <c r="A10" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="B10" s="42"/>
+      <c r="B10" s="47"/>
       <c r="C10" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D10" s="56" t="s">
+      <c r="D10" s="50" t="s">
         <v>18</v>
       </c>
-      <c r="E10" s="57"/>
-      <c r="F10" s="56" t="s">
+      <c r="E10" s="55"/>
+      <c r="F10" s="50" t="s">
         <v>18</v>
       </c>
-      <c r="G10" s="57"/>
+      <c r="G10" s="55"/>
     </row>
     <row r="11" spans="1:7" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="43"/>
-      <c r="B11" s="44"/>
+      <c r="A11" s="48"/>
+      <c r="B11" s="49"/>
       <c r="C11" s="13">
         <v>1</v>
       </c>
-      <c r="D11" s="58" t="s">
+      <c r="D11" s="53" t="s">
         <v>163</v>
       </c>
-      <c r="E11" s="59"/>
-      <c r="F11" s="60" t="s">
+      <c r="E11" s="54"/>
+      <c r="F11" s="57" t="s">
         <v>164</v>
       </c>
-      <c r="G11" s="61"/>
+      <c r="G11" s="58"/>
     </row>
     <row r="12" spans="1:7" ht="42.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="43"/>
-      <c r="B12" s="44"/>
+      <c r="A12" s="48"/>
+      <c r="B12" s="49"/>
       <c r="C12" s="13">
         <v>2</v>
       </c>
-      <c r="D12" s="58" t="s">
+      <c r="D12" s="53" t="s">
         <v>165</v>
       </c>
-      <c r="E12" s="59"/>
-      <c r="F12" s="60" t="s">
+      <c r="E12" s="54"/>
+      <c r="F12" s="57" t="s">
         <v>166</v>
       </c>
-      <c r="G12" s="61"/>
+      <c r="G12" s="58"/>
     </row>
     <row r="13" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="43"/>
-      <c r="B13" s="44"/>
+      <c r="A13" s="48"/>
+      <c r="B13" s="49"/>
       <c r="C13" s="13">
         <v>3</v>
       </c>
-      <c r="D13" s="58" t="s">
+      <c r="D13" s="53" t="s">
         <v>167</v>
       </c>
-      <c r="E13" s="59"/>
-      <c r="F13" s="60" t="s">
+      <c r="E13" s="54"/>
+      <c r="F13" s="57" t="s">
         <v>160</v>
       </c>
-      <c r="G13" s="61"/>
+      <c r="G13" s="58"/>
     </row>
     <row r="14" spans="1:7" ht="45.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="43"/>
-      <c r="B14" s="44"/>
+      <c r="A14" s="48"/>
+      <c r="B14" s="49"/>
       <c r="C14" s="13">
         <v>4</v>
       </c>
-      <c r="D14" s="58"/>
-      <c r="E14" s="59"/>
-      <c r="F14" s="60" t="s">
+      <c r="D14" s="53"/>
+      <c r="E14" s="54"/>
+      <c r="F14" s="57" t="s">
         <v>168</v>
       </c>
-      <c r="G14" s="61"/>
+      <c r="G14" s="58"/>
     </row>
     <row r="15" spans="1:7" ht="45.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="43"/>
-      <c r="B15" s="44"/>
+      <c r="A15" s="48"/>
+      <c r="B15" s="49"/>
       <c r="C15" s="13">
         <v>5</v>
       </c>
-      <c r="D15" s="58"/>
-      <c r="E15" s="59"/>
-      <c r="F15" s="60" t="s">
+      <c r="D15" s="53"/>
+      <c r="E15" s="54"/>
+      <c r="F15" s="57" t="s">
         <v>169</v>
       </c>
-      <c r="G15" s="61"/>
+      <c r="G15" s="58"/>
     </row>
     <row r="16" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
@@ -10075,12 +10075,12 @@
       <c r="C16" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D16" s="21" t="s">
+      <c r="D16" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="E16" s="30"/>
-      <c r="F16" s="30"/>
-      <c r="G16" s="22"/>
+      <c r="E16" s="28"/>
+      <c r="F16" s="28"/>
+      <c r="G16" s="29"/>
     </row>
     <row r="17" spans="1:7" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="9"/>
@@ -10088,12 +10088,12 @@
       <c r="C17" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="D17" s="35" t="s">
+      <c r="D17" s="31" t="s">
         <v>57</v>
       </c>
-      <c r="E17" s="30"/>
-      <c r="F17" s="30"/>
-      <c r="G17" s="22"/>
+      <c r="E17" s="28"/>
+      <c r="F17" s="28"/>
+      <c r="G17" s="29"/>
     </row>
     <row r="18" spans="1:7" ht="51.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="11"/>
@@ -10101,25 +10101,25 @@
       <c r="C18" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="D18" s="35" t="s">
+      <c r="D18" s="31" t="s">
         <v>58</v>
       </c>
-      <c r="E18" s="30"/>
-      <c r="F18" s="30"/>
-      <c r="G18" s="22"/>
+      <c r="E18" s="28"/>
+      <c r="F18" s="28"/>
+      <c r="G18" s="29"/>
     </row>
     <row r="19" spans="1:7" ht="35.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="27" t="s">
+      <c r="A19" s="41" t="s">
         <v>26</v>
       </c>
-      <c r="B19" s="22"/>
-      <c r="C19" s="35" t="s">
+      <c r="B19" s="29"/>
+      <c r="C19" s="31" t="s">
         <v>56</v>
       </c>
-      <c r="D19" s="30"/>
-      <c r="E19" s="30"/>
-      <c r="F19" s="30"/>
-      <c r="G19" s="22"/>
+      <c r="D19" s="28"/>
+      <c r="E19" s="28"/>
+      <c r="F19" s="28"/>
+      <c r="G19" s="29"/>
     </row>
     <row r="20" spans="1:7" ht="66" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="21" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -10816,22 +10816,9 @@
     <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="35">
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="D17:G17"/>
-    <mergeCell ref="D18:G18"/>
-    <mergeCell ref="C19:G19"/>
-    <mergeCell ref="D16:G16"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="A6:B7"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A9:B9"/>
     <mergeCell ref="A10:B15"/>
     <mergeCell ref="A19:B19"/>
     <mergeCell ref="A1:B1"/>
@@ -10848,9 +10835,22 @@
     <mergeCell ref="C9:G9"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A6:B7"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="D17:G17"/>
+    <mergeCell ref="D18:G18"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="D16:G16"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="F12:G12"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -10869,28 +10869,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="21" t="s">
+      <c r="B1" s="29"/>
+      <c r="C1" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="22"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="29"/>
     </row>
     <row r="2" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="22"/>
-      <c r="C2" s="38" t="s">
+      <c r="B2" s="29"/>
+      <c r="C2" s="56" t="s">
         <v>59</v>
       </c>
-      <c r="D2" s="30"/>
-      <c r="E2" s="22"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="29"/>
       <c r="F2" s="1" t="s">
         <v>4</v>
       </c>
@@ -10899,185 +10899,185 @@
       </c>
     </row>
     <row r="3" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A3" s="21" t="s">
+      <c r="A3" s="32" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="22"/>
-      <c r="C3" s="31" t="s">
+      <c r="B3" s="29"/>
+      <c r="C3" s="27" t="s">
         <v>28</v>
       </c>
-      <c r="D3" s="30"/>
-      <c r="E3" s="30"/>
-      <c r="F3" s="30"/>
-      <c r="G3" s="22"/>
+      <c r="D3" s="28"/>
+      <c r="E3" s="28"/>
+      <c r="F3" s="28"/>
+      <c r="G3" s="29"/>
     </row>
     <row r="4" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A4" s="21" t="s">
+      <c r="A4" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="22"/>
-      <c r="C4" s="32">
+      <c r="B4" s="29"/>
+      <c r="C4" s="42">
         <v>45789</v>
       </c>
-      <c r="D4" s="30"/>
-      <c r="E4" s="30"/>
-      <c r="F4" s="30"/>
-      <c r="G4" s="22"/>
+      <c r="D4" s="28"/>
+      <c r="E4" s="28"/>
+      <c r="F4" s="28"/>
+      <c r="G4" s="29"/>
     </row>
     <row r="5" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A5" s="21" t="s">
+      <c r="A5" s="32" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="22"/>
-      <c r="C5" s="37" t="s">
+      <c r="B5" s="29"/>
+      <c r="C5" s="66" t="s">
         <v>60</v>
       </c>
-      <c r="D5" s="30"/>
-      <c r="E5" s="30"/>
-      <c r="F5" s="30"/>
-      <c r="G5" s="22"/>
+      <c r="D5" s="28"/>
+      <c r="E5" s="28"/>
+      <c r="F5" s="28"/>
+      <c r="G5" s="29"/>
     </row>
     <row r="6" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A6" s="23" t="s">
+      <c r="A6" s="35" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="24"/>
+      <c r="B6" s="36"/>
       <c r="C6" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D6" s="31" t="s">
+      <c r="D6" s="27" t="s">
         <v>30</v>
       </c>
-      <c r="E6" s="30"/>
-      <c r="F6" s="30"/>
-      <c r="G6" s="22"/>
+      <c r="E6" s="28"/>
+      <c r="F6" s="28"/>
+      <c r="G6" s="29"/>
     </row>
     <row r="7" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A7" s="25"/>
-      <c r="B7" s="26"/>
+      <c r="A7" s="39"/>
+      <c r="B7" s="40"/>
       <c r="C7" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D7" s="38" t="s">
+      <c r="D7" s="56" t="s">
         <v>61</v>
       </c>
-      <c r="E7" s="30"/>
-      <c r="F7" s="30"/>
-      <c r="G7" s="22"/>
+      <c r="E7" s="28"/>
+      <c r="F7" s="28"/>
+      <c r="G7" s="29"/>
     </row>
     <row r="8" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="27" t="s">
+      <c r="A8" s="41" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="22"/>
-      <c r="C8" s="35" t="s">
+      <c r="B8" s="29"/>
+      <c r="C8" s="31" t="s">
         <v>62</v>
       </c>
-      <c r="D8" s="30"/>
-      <c r="E8" s="30"/>
-      <c r="F8" s="30"/>
-      <c r="G8" s="22"/>
+      <c r="D8" s="28"/>
+      <c r="E8" s="28"/>
+      <c r="F8" s="28"/>
+      <c r="G8" s="29"/>
     </row>
     <row r="9" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="27" t="s">
+      <c r="A9" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="22"/>
-      <c r="C9" s="35" t="s">
+      <c r="B9" s="29"/>
+      <c r="C9" s="31" t="s">
         <v>45</v>
       </c>
-      <c r="D9" s="30"/>
-      <c r="E9" s="30"/>
-      <c r="F9" s="30"/>
-      <c r="G9" s="22"/>
+      <c r="D9" s="28"/>
+      <c r="E9" s="28"/>
+      <c r="F9" s="28"/>
+      <c r="G9" s="29"/>
     </row>
     <row r="10" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A10" s="41" t="s">
+      <c r="A10" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="B10" s="42"/>
+      <c r="B10" s="47"/>
       <c r="C10" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D10" s="56" t="s">
+      <c r="D10" s="50" t="s">
         <v>18</v>
       </c>
-      <c r="E10" s="65"/>
-      <c r="F10" s="56" t="s">
+      <c r="E10" s="62"/>
+      <c r="F10" s="50" t="s">
         <v>18</v>
       </c>
-      <c r="G10" s="57"/>
+      <c r="G10" s="55"/>
     </row>
     <row r="11" spans="1:7" ht="44.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="43"/>
-      <c r="B11" s="44"/>
+      <c r="A11" s="48"/>
+      <c r="B11" s="49"/>
       <c r="C11" s="13">
         <v>1</v>
       </c>
-      <c r="D11" s="58" t="s">
+      <c r="D11" s="53" t="s">
         <v>170</v>
       </c>
-      <c r="E11" s="59"/>
-      <c r="F11" s="60" t="s">
+      <c r="E11" s="54"/>
+      <c r="F11" s="57" t="s">
         <v>171</v>
       </c>
-      <c r="G11" s="64"/>
+      <c r="G11" s="63"/>
     </row>
     <row r="12" spans="1:7" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="43"/>
-      <c r="B12" s="44"/>
+      <c r="A12" s="48"/>
+      <c r="B12" s="49"/>
       <c r="C12" s="13">
         <v>2</v>
       </c>
-      <c r="D12" s="58" t="s">
+      <c r="D12" s="53" t="s">
         <v>172</v>
       </c>
-      <c r="E12" s="59"/>
-      <c r="F12" s="60" t="s">
+      <c r="E12" s="54"/>
+      <c r="F12" s="57" t="s">
         <v>166</v>
       </c>
-      <c r="G12" s="64"/>
+      <c r="G12" s="63"/>
     </row>
     <row r="13" spans="1:7" ht="78" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="43"/>
-      <c r="B13" s="44"/>
+      <c r="A13" s="48"/>
+      <c r="B13" s="49"/>
       <c r="C13" s="13">
         <v>3</v>
       </c>
-      <c r="D13" s="58" t="s">
+      <c r="D13" s="53" t="s">
         <v>173</v>
       </c>
-      <c r="E13" s="59"/>
-      <c r="F13" s="60" t="s">
+      <c r="E13" s="54"/>
+      <c r="F13" s="57" t="s">
         <v>174</v>
       </c>
-      <c r="G13" s="64"/>
+      <c r="G13" s="63"/>
     </row>
     <row r="14" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="43"/>
-      <c r="B14" s="44"/>
+      <c r="A14" s="48"/>
+      <c r="B14" s="49"/>
       <c r="C14" s="13">
         <v>4</v>
       </c>
-      <c r="D14" s="58"/>
-      <c r="E14" s="59"/>
-      <c r="F14" s="60" t="s">
+      <c r="D14" s="53"/>
+      <c r="E14" s="54"/>
+      <c r="F14" s="57" t="s">
         <v>175</v>
       </c>
-      <c r="G14" s="64"/>
+      <c r="G14" s="63"/>
     </row>
     <row r="15" spans="1:7" ht="45.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="43"/>
-      <c r="B15" s="44"/>
+      <c r="A15" s="48"/>
+      <c r="B15" s="49"/>
       <c r="C15" s="13">
         <v>5</v>
       </c>
-      <c r="D15" s="58"/>
-      <c r="E15" s="59"/>
-      <c r="F15" s="60" t="s">
+      <c r="D15" s="53"/>
+      <c r="E15" s="54"/>
+      <c r="F15" s="57" t="s">
         <v>176</v>
       </c>
-      <c r="G15" s="64"/>
+      <c r="G15" s="63"/>
     </row>
     <row r="16" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="14" t="s">
@@ -11087,12 +11087,12 @@
       <c r="C16" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D16" s="21" t="s">
+      <c r="D16" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="E16" s="62"/>
-      <c r="F16" s="62"/>
-      <c r="G16" s="63"/>
+      <c r="E16" s="64"/>
+      <c r="F16" s="64"/>
+      <c r="G16" s="65"/>
     </row>
     <row r="17" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="19"/>
@@ -11100,25 +11100,25 @@
       <c r="C17" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="D17" s="35" t="s">
+      <c r="D17" s="31" t="s">
         <v>64</v>
       </c>
-      <c r="E17" s="46"/>
-      <c r="F17" s="46"/>
-      <c r="G17" s="47"/>
+      <c r="E17" s="60"/>
+      <c r="F17" s="60"/>
+      <c r="G17" s="61"/>
     </row>
     <row r="18" spans="1:7" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="27" t="s">
+      <c r="A18" s="41" t="s">
         <v>26</v>
       </c>
-      <c r="B18" s="45"/>
-      <c r="C18" s="35" t="s">
+      <c r="B18" s="59"/>
+      <c r="C18" s="31" t="s">
         <v>63</v>
       </c>
-      <c r="D18" s="46"/>
-      <c r="E18" s="46"/>
-      <c r="F18" s="46"/>
-      <c r="G18" s="47"/>
+      <c r="D18" s="60"/>
+      <c r="E18" s="60"/>
+      <c r="F18" s="60"/>
+      <c r="G18" s="61"/>
     </row>
     <row r="19" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="20" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -11819,6 +11819,24 @@
     <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="34">
+    <mergeCell ref="A10:B15"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A6:B7"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="C4:G4"/>
+    <mergeCell ref="C5:G5"/>
+    <mergeCell ref="D6:G6"/>
+    <mergeCell ref="D7:G7"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:G1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:E2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="C3:G3"/>
     <mergeCell ref="A18:B18"/>
     <mergeCell ref="C18:G18"/>
     <mergeCell ref="D10:E10"/>
@@ -11835,24 +11853,6 @@
     <mergeCell ref="F14:G14"/>
     <mergeCell ref="D15:E15"/>
     <mergeCell ref="F15:G15"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:G1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:E2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="C4:G4"/>
-    <mergeCell ref="C5:G5"/>
-    <mergeCell ref="D6:G6"/>
-    <mergeCell ref="D7:G7"/>
-    <mergeCell ref="C8:G8"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A6:B7"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="A10:B15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -11870,28 +11870,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="21" t="s">
+      <c r="B1" s="29"/>
+      <c r="C1" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="22"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="29"/>
     </row>
     <row r="2" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="22"/>
-      <c r="C2" s="31" t="s">
+      <c r="B2" s="29"/>
+      <c r="C2" s="27" t="s">
         <v>65</v>
       </c>
-      <c r="D2" s="30"/>
-      <c r="E2" s="22"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="29"/>
       <c r="F2" s="1" t="s">
         <v>4</v>
       </c>
@@ -11900,278 +11900,278 @@
       </c>
     </row>
     <row r="3" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A3" s="21" t="s">
+      <c r="A3" s="32" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="22"/>
-      <c r="C3" s="31" t="s">
+      <c r="B3" s="29"/>
+      <c r="C3" s="27" t="s">
         <v>28</v>
       </c>
-      <c r="D3" s="30"/>
-      <c r="E3" s="30"/>
-      <c r="F3" s="30"/>
-      <c r="G3" s="22"/>
+      <c r="D3" s="28"/>
+      <c r="E3" s="28"/>
+      <c r="F3" s="28"/>
+      <c r="G3" s="29"/>
     </row>
     <row r="4" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A4" s="21" t="s">
+      <c r="A4" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="22"/>
-      <c r="C4" s="32">
+      <c r="B4" s="29"/>
+      <c r="C4" s="42">
         <v>45789</v>
       </c>
-      <c r="D4" s="30"/>
-      <c r="E4" s="30"/>
-      <c r="F4" s="30"/>
-      <c r="G4" s="22"/>
+      <c r="D4" s="28"/>
+      <c r="E4" s="28"/>
+      <c r="F4" s="28"/>
+      <c r="G4" s="29"/>
     </row>
     <row r="5" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A5" s="21" t="s">
+      <c r="A5" s="32" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="22"/>
-      <c r="C5" s="31" t="s">
+      <c r="B5" s="29"/>
+      <c r="C5" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="D5" s="30"/>
-      <c r="E5" s="30"/>
-      <c r="F5" s="30"/>
-      <c r="G5" s="22"/>
+      <c r="D5" s="28"/>
+      <c r="E5" s="28"/>
+      <c r="F5" s="28"/>
+      <c r="G5" s="29"/>
     </row>
     <row r="6" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A6" s="23" t="s">
+      <c r="A6" s="35" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="24"/>
+      <c r="B6" s="36"/>
       <c r="C6" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D6" s="31" t="s">
+      <c r="D6" s="27" t="s">
         <v>66</v>
       </c>
-      <c r="E6" s="30"/>
-      <c r="F6" s="30"/>
-      <c r="G6" s="22"/>
+      <c r="E6" s="28"/>
+      <c r="F6" s="28"/>
+      <c r="G6" s="29"/>
     </row>
     <row r="7" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A7" s="25"/>
-      <c r="B7" s="26"/>
+      <c r="A7" s="39"/>
+      <c r="B7" s="40"/>
       <c r="C7" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D7" s="31"/>
-      <c r="E7" s="30"/>
-      <c r="F7" s="30"/>
-      <c r="G7" s="22"/>
+      <c r="D7" s="27"/>
+      <c r="E7" s="28"/>
+      <c r="F7" s="28"/>
+      <c r="G7" s="29"/>
     </row>
     <row r="8" spans="1:7" ht="43.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="27" t="s">
+      <c r="A8" s="41" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="22"/>
-      <c r="C8" s="36" t="s">
+      <c r="B8" s="29"/>
+      <c r="C8" s="30" t="s">
         <v>67</v>
       </c>
-      <c r="D8" s="30"/>
-      <c r="E8" s="30"/>
-      <c r="F8" s="30"/>
-      <c r="G8" s="22"/>
+      <c r="D8" s="28"/>
+      <c r="E8" s="28"/>
+      <c r="F8" s="28"/>
+      <c r="G8" s="29"/>
     </row>
     <row r="9" spans="1:7" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="27" t="s">
+      <c r="A9" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="22"/>
-      <c r="C9" s="36" t="s">
+      <c r="B9" s="29"/>
+      <c r="C9" s="30" t="s">
         <v>68</v>
       </c>
-      <c r="D9" s="30"/>
-      <c r="E9" s="30"/>
-      <c r="F9" s="30"/>
-      <c r="G9" s="22"/>
+      <c r="D9" s="28"/>
+      <c r="E9" s="28"/>
+      <c r="F9" s="28"/>
+      <c r="G9" s="29"/>
     </row>
     <row r="10" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A10" s="41" t="s">
+      <c r="A10" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="B10" s="42"/>
+      <c r="B10" s="47"/>
       <c r="C10" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D10" s="56" t="s">
+      <c r="D10" s="50" t="s">
         <v>18</v>
       </c>
-      <c r="E10" s="57"/>
-      <c r="F10" s="56" t="s">
+      <c r="E10" s="55"/>
+      <c r="F10" s="50" t="s">
         <v>18</v>
       </c>
-      <c r="G10" s="57"/>
+      <c r="G10" s="55"/>
     </row>
     <row r="11" spans="1:7" ht="75.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="43"/>
-      <c r="B11" s="44"/>
+      <c r="A11" s="48"/>
+      <c r="B11" s="49"/>
       <c r="C11" s="13">
         <v>1</v>
       </c>
-      <c r="D11" s="58" t="s">
+      <c r="D11" s="53" t="s">
         <v>177</v>
       </c>
-      <c r="E11" s="59"/>
-      <c r="F11" s="60"/>
-      <c r="G11" s="61"/>
+      <c r="E11" s="54"/>
+      <c r="F11" s="57"/>
+      <c r="G11" s="58"/>
     </row>
     <row r="12" spans="1:7" ht="66.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="43"/>
-      <c r="B12" s="44"/>
+      <c r="A12" s="48"/>
+      <c r="B12" s="49"/>
       <c r="C12" s="13">
         <v>2</v>
       </c>
-      <c r="D12" s="58" t="s">
+      <c r="D12" s="53" t="s">
         <v>178</v>
       </c>
-      <c r="E12" s="59"/>
-      <c r="F12" s="60" t="s">
+      <c r="E12" s="54"/>
+      <c r="F12" s="57" t="s">
         <v>179</v>
       </c>
-      <c r="G12" s="61"/>
+      <c r="G12" s="58"/>
     </row>
     <row r="13" spans="1:7" ht="48" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="43"/>
-      <c r="B13" s="44"/>
+      <c r="A13" s="48"/>
+      <c r="B13" s="49"/>
       <c r="C13" s="13">
         <v>3</v>
       </c>
-      <c r="D13" s="58" t="s">
+      <c r="D13" s="53" t="s">
         <v>180</v>
       </c>
-      <c r="E13" s="59"/>
-      <c r="F13" s="60"/>
-      <c r="G13" s="61"/>
+      <c r="E13" s="54"/>
+      <c r="F13" s="57"/>
+      <c r="G13" s="58"/>
     </row>
     <row r="14" spans="1:7" ht="66" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="43"/>
-      <c r="B14" s="44"/>
+      <c r="A14" s="48"/>
+      <c r="B14" s="49"/>
       <c r="C14" s="13">
         <v>4</v>
       </c>
-      <c r="D14" s="58" t="s">
+      <c r="D14" s="53" t="s">
         <v>181</v>
       </c>
-      <c r="E14" s="59"/>
-      <c r="F14" s="60" t="s">
+      <c r="E14" s="54"/>
+      <c r="F14" s="57" t="s">
         <v>182</v>
       </c>
-      <c r="G14" s="61"/>
+      <c r="G14" s="58"/>
     </row>
     <row r="15" spans="1:7" ht="49.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="43"/>
-      <c r="B15" s="44"/>
+      <c r="A15" s="48"/>
+      <c r="B15" s="49"/>
       <c r="C15" s="13">
         <v>5</v>
       </c>
-      <c r="D15" s="58" t="s">
+      <c r="D15" s="53" t="s">
         <v>183</v>
       </c>
-      <c r="E15" s="59"/>
-      <c r="F15" s="60"/>
-      <c r="G15" s="61"/>
+      <c r="E15" s="54"/>
+      <c r="F15" s="57"/>
+      <c r="G15" s="58"/>
     </row>
     <row r="16" spans="1:7" ht="69" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="43"/>
-      <c r="B16" s="44"/>
+      <c r="A16" s="48"/>
+      <c r="B16" s="49"/>
       <c r="C16" s="13">
         <v>6</v>
       </c>
-      <c r="D16" s="58" t="s">
+      <c r="D16" s="53" t="s">
         <v>184</v>
       </c>
-      <c r="E16" s="59"/>
-      <c r="F16" s="60" t="s">
+      <c r="E16" s="54"/>
+      <c r="F16" s="57" t="s">
         <v>185</v>
       </c>
-      <c r="G16" s="61"/>
+      <c r="G16" s="58"/>
     </row>
     <row r="17" spans="1:7" ht="85.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="43"/>
-      <c r="B17" s="44"/>
+      <c r="A17" s="48"/>
+      <c r="B17" s="49"/>
       <c r="C17" s="13">
         <v>7</v>
       </c>
-      <c r="D17" s="54" t="s">
+      <c r="D17" s="24" t="s">
         <v>186</v>
       </c>
-      <c r="E17" s="55"/>
-      <c r="F17" s="60" t="s">
+      <c r="E17" s="45"/>
+      <c r="F17" s="57" t="s">
         <v>187</v>
       </c>
-      <c r="G17" s="61"/>
+      <c r="G17" s="58"/>
     </row>
     <row r="18" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="23" t="s">
+      <c r="A18" s="35" t="s">
         <v>19</v>
       </c>
-      <c r="B18" s="24"/>
+      <c r="B18" s="36"/>
       <c r="C18" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D18" s="21" t="s">
+      <c r="D18" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="E18" s="30"/>
-      <c r="F18" s="30"/>
-      <c r="G18" s="22"/>
+      <c r="E18" s="28"/>
+      <c r="F18" s="28"/>
+      <c r="G18" s="29"/>
     </row>
     <row r="19" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="28"/>
-      <c r="B19" s="29"/>
+      <c r="A19" s="37"/>
+      <c r="B19" s="38"/>
       <c r="C19" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="D19" s="35" t="s">
+      <c r="D19" s="31" t="s">
         <v>70</v>
       </c>
-      <c r="E19" s="30"/>
-      <c r="F19" s="30"/>
-      <c r="G19" s="22"/>
+      <c r="E19" s="28"/>
+      <c r="F19" s="28"/>
+      <c r="G19" s="29"/>
     </row>
     <row r="20" spans="1:7" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="28"/>
-      <c r="B20" s="29"/>
+      <c r="A20" s="37"/>
+      <c r="B20" s="38"/>
       <c r="C20" s="16" t="s">
         <v>74</v>
       </c>
-      <c r="D20" s="35" t="s">
+      <c r="D20" s="31" t="s">
         <v>71</v>
       </c>
-      <c r="E20" s="30"/>
-      <c r="F20" s="30"/>
-      <c r="G20" s="22"/>
+      <c r="E20" s="28"/>
+      <c r="F20" s="28"/>
+      <c r="G20" s="29"/>
     </row>
     <row r="21" spans="1:7" ht="31.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="25"/>
-      <c r="B21" s="26"/>
+      <c r="A21" s="39"/>
+      <c r="B21" s="40"/>
       <c r="C21" s="16" t="s">
         <v>75</v>
       </c>
-      <c r="D21" s="35" t="s">
+      <c r="D21" s="31" t="s">
         <v>72</v>
       </c>
-      <c r="E21" s="30"/>
-      <c r="F21" s="30"/>
-      <c r="G21" s="22"/>
+      <c r="E21" s="28"/>
+      <c r="F21" s="28"/>
+      <c r="G21" s="29"/>
     </row>
     <row r="22" spans="1:7" ht="78" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="27" t="s">
+      <c r="A22" s="41" t="s">
         <v>26</v>
       </c>
-      <c r="B22" s="22"/>
-      <c r="C22" s="36" t="s">
+      <c r="B22" s="29"/>
+      <c r="C22" s="30" t="s">
         <v>69</v>
       </c>
-      <c r="D22" s="30"/>
-      <c r="E22" s="30"/>
-      <c r="F22" s="30"/>
-      <c r="G22" s="22"/>
+      <c r="D22" s="28"/>
+      <c r="E22" s="28"/>
+      <c r="F22" s="28"/>
+      <c r="G22" s="29"/>
     </row>
     <row r="23" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="24" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -12868,33 +12868,6 @@
     <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="41">
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="C4:G4"/>
-    <mergeCell ref="C5:G5"/>
-    <mergeCell ref="D6:G6"/>
-    <mergeCell ref="D7:G7"/>
-    <mergeCell ref="C8:G8"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:G1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:E2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A6:B7"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="A9:B9"/>
     <mergeCell ref="A22:B22"/>
     <mergeCell ref="C22:G22"/>
     <mergeCell ref="A10:B17"/>
@@ -12909,6 +12882,33 @@
     <mergeCell ref="F13:G13"/>
     <mergeCell ref="D14:E14"/>
     <mergeCell ref="F14:G14"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A6:B7"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:G1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:E2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C4:G4"/>
+    <mergeCell ref="C5:G5"/>
+    <mergeCell ref="D6:G6"/>
+    <mergeCell ref="D7:G7"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="F17:G17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -12926,28 +12926,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="21" t="s">
+      <c r="B1" s="29"/>
+      <c r="C1" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="22"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="29"/>
     </row>
     <row r="2" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="22"/>
-      <c r="C2" s="38" t="s">
+      <c r="B2" s="29"/>
+      <c r="C2" s="56" t="s">
         <v>76</v>
       </c>
-      <c r="D2" s="30"/>
-      <c r="E2" s="22"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="29"/>
       <c r="F2" s="1" t="s">
         <v>4</v>
       </c>
@@ -12956,213 +12956,213 @@
       </c>
     </row>
     <row r="3" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A3" s="21" t="s">
+      <c r="A3" s="32" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="22"/>
-      <c r="C3" s="31" t="s">
+      <c r="B3" s="29"/>
+      <c r="C3" s="27" t="s">
         <v>28</v>
       </c>
-      <c r="D3" s="30"/>
-      <c r="E3" s="30"/>
-      <c r="F3" s="30"/>
-      <c r="G3" s="22"/>
+      <c r="D3" s="28"/>
+      <c r="E3" s="28"/>
+      <c r="F3" s="28"/>
+      <c r="G3" s="29"/>
     </row>
     <row r="4" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A4" s="21" t="s">
+      <c r="A4" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="22"/>
-      <c r="C4" s="32">
+      <c r="B4" s="29"/>
+      <c r="C4" s="42">
         <v>45789</v>
       </c>
-      <c r="D4" s="30"/>
-      <c r="E4" s="30"/>
-      <c r="F4" s="30"/>
-      <c r="G4" s="22"/>
+      <c r="D4" s="28"/>
+      <c r="E4" s="28"/>
+      <c r="F4" s="28"/>
+      <c r="G4" s="29"/>
     </row>
     <row r="5" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A5" s="21" t="s">
+      <c r="A5" s="32" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="22"/>
-      <c r="C5" s="37" t="s">
+      <c r="B5" s="29"/>
+      <c r="C5" s="66" t="s">
         <v>29</v>
       </c>
-      <c r="D5" s="30"/>
-      <c r="E5" s="30"/>
-      <c r="F5" s="30"/>
-      <c r="G5" s="22"/>
+      <c r="D5" s="28"/>
+      <c r="E5" s="28"/>
+      <c r="F5" s="28"/>
+      <c r="G5" s="29"/>
     </row>
     <row r="6" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A6" s="23" t="s">
+      <c r="A6" s="35" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="24"/>
+      <c r="B6" s="36"/>
       <c r="C6" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D6" s="38" t="s">
+      <c r="D6" s="56" t="s">
         <v>77</v>
       </c>
-      <c r="E6" s="30"/>
-      <c r="F6" s="30"/>
-      <c r="G6" s="22"/>
+      <c r="E6" s="28"/>
+      <c r="F6" s="28"/>
+      <c r="G6" s="29"/>
     </row>
     <row r="7" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A7" s="25"/>
-      <c r="B7" s="26"/>
+      <c r="A7" s="39"/>
+      <c r="B7" s="40"/>
       <c r="C7" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D7" s="31"/>
-      <c r="E7" s="30"/>
-      <c r="F7" s="30"/>
-      <c r="G7" s="22"/>
+      <c r="D7" s="27"/>
+      <c r="E7" s="28"/>
+      <c r="F7" s="28"/>
+      <c r="G7" s="29"/>
     </row>
     <row r="8" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="27" t="s">
+      <c r="A8" s="41" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="22"/>
-      <c r="C8" s="35" t="s">
+      <c r="B8" s="29"/>
+      <c r="C8" s="31" t="s">
         <v>78</v>
       </c>
-      <c r="D8" s="30"/>
-      <c r="E8" s="30"/>
-      <c r="F8" s="30"/>
-      <c r="G8" s="22"/>
+      <c r="D8" s="28"/>
+      <c r="E8" s="28"/>
+      <c r="F8" s="28"/>
+      <c r="G8" s="29"/>
     </row>
     <row r="9" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="27" t="s">
+      <c r="A9" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="22"/>
-      <c r="C9" s="35" t="s">
+      <c r="B9" s="29"/>
+      <c r="C9" s="31" t="s">
         <v>79</v>
       </c>
-      <c r="D9" s="30"/>
-      <c r="E9" s="30"/>
-      <c r="F9" s="30"/>
-      <c r="G9" s="22"/>
+      <c r="D9" s="28"/>
+      <c r="E9" s="28"/>
+      <c r="F9" s="28"/>
+      <c r="G9" s="29"/>
     </row>
     <row r="10" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A10" s="23" t="s">
+      <c r="A10" s="35" t="s">
         <v>16</v>
       </c>
-      <c r="B10" s="24"/>
+      <c r="B10" s="36"/>
       <c r="C10" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D10" s="56" t="s">
+      <c r="D10" s="50" t="s">
         <v>137</v>
       </c>
-      <c r="E10" s="49"/>
-      <c r="F10" s="56" t="s">
+      <c r="E10" s="34"/>
+      <c r="F10" s="50" t="s">
         <v>138</v>
       </c>
-      <c r="G10" s="49"/>
+      <c r="G10" s="34"/>
     </row>
     <row r="11" spans="1:7" ht="63.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="28"/>
-      <c r="B11" s="29"/>
+      <c r="A11" s="37"/>
+      <c r="B11" s="38"/>
       <c r="C11" s="13">
         <v>1</v>
       </c>
-      <c r="D11" s="52" t="s">
+      <c r="D11" s="22" t="s">
         <v>188</v>
       </c>
-      <c r="E11" s="53"/>
-      <c r="F11" s="52" t="s">
+      <c r="E11" s="23"/>
+      <c r="F11" s="22" t="s">
         <v>189</v>
       </c>
-      <c r="G11" s="53"/>
+      <c r="G11" s="23"/>
     </row>
     <row r="12" spans="1:7" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="28"/>
-      <c r="B12" s="29"/>
+      <c r="A12" s="37"/>
+      <c r="B12" s="38"/>
       <c r="C12" s="13">
         <v>2</v>
       </c>
-      <c r="D12" s="52" t="s">
+      <c r="D12" s="22" t="s">
         <v>190</v>
       </c>
-      <c r="E12" s="53"/>
-      <c r="F12" s="52" t="s">
+      <c r="E12" s="23"/>
+      <c r="F12" s="22" t="s">
         <v>191</v>
       </c>
-      <c r="G12" s="53"/>
+      <c r="G12" s="23"/>
     </row>
     <row r="13" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="28"/>
-      <c r="B13" s="29"/>
+      <c r="A13" s="37"/>
+      <c r="B13" s="38"/>
       <c r="C13" s="13">
         <v>3</v>
       </c>
-      <c r="D13" s="52" t="s">
+      <c r="D13" s="22" t="s">
         <v>192</v>
       </c>
-      <c r="E13" s="53"/>
-      <c r="F13" s="52" t="s">
+      <c r="E13" s="23"/>
+      <c r="F13" s="22" t="s">
         <v>193</v>
       </c>
-      <c r="G13" s="53"/>
+      <c r="G13" s="23"/>
     </row>
     <row r="14" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="28"/>
-      <c r="B14" s="29"/>
+      <c r="A14" s="37"/>
+      <c r="B14" s="38"/>
       <c r="C14" s="13">
         <v>4</v>
       </c>
-      <c r="D14" s="52" t="s">
+      <c r="D14" s="22" t="s">
         <v>194</v>
       </c>
-      <c r="E14" s="53"/>
-      <c r="F14" s="52" t="s">
+      <c r="E14" s="23"/>
+      <c r="F14" s="22" t="s">
         <v>195</v>
       </c>
-      <c r="G14" s="53"/>
+      <c r="G14" s="23"/>
     </row>
     <row r="15" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="23" t="s">
+      <c r="A15" s="35" t="s">
         <v>19</v>
       </c>
-      <c r="B15" s="24"/>
+      <c r="B15" s="36"/>
       <c r="C15" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D15" s="21" t="s">
+      <c r="D15" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="E15" s="30"/>
-      <c r="F15" s="30"/>
-      <c r="G15" s="22"/>
+      <c r="E15" s="28"/>
+      <c r="F15" s="28"/>
+      <c r="G15" s="29"/>
     </row>
     <row r="16" spans="1:7" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="28"/>
-      <c r="B16" s="29"/>
+      <c r="A16" s="37"/>
+      <c r="B16" s="38"/>
       <c r="C16" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="D16" s="35" t="s">
+      <c r="D16" s="31" t="s">
         <v>81</v>
       </c>
-      <c r="E16" s="30"/>
-      <c r="F16" s="30"/>
-      <c r="G16" s="22"/>
+      <c r="E16" s="28"/>
+      <c r="F16" s="28"/>
+      <c r="G16" s="29"/>
     </row>
     <row r="17" spans="1:7" ht="49.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="27" t="s">
+      <c r="A17" s="41" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="22"/>
-      <c r="C17" s="35" t="s">
+      <c r="B17" s="29"/>
+      <c r="C17" s="31" t="s">
         <v>80</v>
       </c>
-      <c r="D17" s="30"/>
-      <c r="E17" s="30"/>
-      <c r="F17" s="30"/>
-      <c r="G17" s="22"/>
+      <c r="D17" s="28"/>
+      <c r="E17" s="28"/>
+      <c r="F17" s="28"/>
+      <c r="G17" s="29"/>
     </row>
     <row r="18" spans="1:7" ht="65.25" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="19" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -13861,19 +13861,10 @@
     <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="33">
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="C17:G17"/>
-    <mergeCell ref="D15:G15"/>
-    <mergeCell ref="D16:G16"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A6:B7"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A9:B9"/>
     <mergeCell ref="A10:B14"/>
     <mergeCell ref="A15:B16"/>
     <mergeCell ref="A17:B17"/>
@@ -13890,10 +13881,19 @@
     <mergeCell ref="C8:G8"/>
     <mergeCell ref="C9:G9"/>
     <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A6:B7"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="C17:G17"/>
+    <mergeCell ref="D15:G15"/>
+    <mergeCell ref="D16:G16"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="F12:G12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -13911,28 +13911,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="21" t="s">
+      <c r="B1" s="29"/>
+      <c r="C1" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="22"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="29"/>
     </row>
     <row r="2" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="22"/>
-      <c r="C2" s="38" t="s">
+      <c r="B2" s="29"/>
+      <c r="C2" s="56" t="s">
         <v>82</v>
       </c>
-      <c r="D2" s="30"/>
-      <c r="E2" s="22"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="29"/>
       <c r="F2" s="1" t="s">
         <v>4</v>
       </c>
@@ -13941,263 +13941,263 @@
       </c>
     </row>
     <row r="3" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A3" s="21" t="s">
+      <c r="A3" s="32" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="22"/>
-      <c r="C3" s="31" t="s">
+      <c r="B3" s="29"/>
+      <c r="C3" s="27" t="s">
         <v>28</v>
       </c>
-      <c r="D3" s="30"/>
-      <c r="E3" s="30"/>
-      <c r="F3" s="30"/>
-      <c r="G3" s="22"/>
+      <c r="D3" s="28"/>
+      <c r="E3" s="28"/>
+      <c r="F3" s="28"/>
+      <c r="G3" s="29"/>
     </row>
     <row r="4" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A4" s="21" t="s">
+      <c r="A4" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="22"/>
-      <c r="C4" s="32">
+      <c r="B4" s="29"/>
+      <c r="C4" s="42">
         <v>45789</v>
       </c>
-      <c r="D4" s="30"/>
-      <c r="E4" s="30"/>
-      <c r="F4" s="30"/>
-      <c r="G4" s="22"/>
+      <c r="D4" s="28"/>
+      <c r="E4" s="28"/>
+      <c r="F4" s="28"/>
+      <c r="G4" s="29"/>
     </row>
     <row r="5" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A5" s="21" t="s">
+      <c r="A5" s="32" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="22"/>
-      <c r="C5" s="31" t="s">
+      <c r="B5" s="29"/>
+      <c r="C5" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="D5" s="30"/>
-      <c r="E5" s="30"/>
-      <c r="F5" s="30"/>
-      <c r="G5" s="22"/>
+      <c r="D5" s="28"/>
+      <c r="E5" s="28"/>
+      <c r="F5" s="28"/>
+      <c r="G5" s="29"/>
     </row>
     <row r="6" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A6" s="23" t="s">
+      <c r="A6" s="35" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="24"/>
+      <c r="B6" s="36"/>
       <c r="C6" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D6" s="38" t="s">
+      <c r="D6" s="56" t="s">
         <v>83</v>
       </c>
-      <c r="E6" s="30"/>
-      <c r="F6" s="30"/>
-      <c r="G6" s="22"/>
+      <c r="E6" s="28"/>
+      <c r="F6" s="28"/>
+      <c r="G6" s="29"/>
     </row>
     <row r="7" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A7" s="25"/>
-      <c r="B7" s="26"/>
+      <c r="A7" s="39"/>
+      <c r="B7" s="40"/>
       <c r="C7" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D7" s="31"/>
-      <c r="E7" s="30"/>
-      <c r="F7" s="30"/>
-      <c r="G7" s="22"/>
+      <c r="D7" s="27"/>
+      <c r="E7" s="28"/>
+      <c r="F7" s="28"/>
+      <c r="G7" s="29"/>
     </row>
     <row r="8" spans="1:7" ht="47.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="27" t="s">
+      <c r="A8" s="41" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="22"/>
-      <c r="C8" s="35" t="s">
+      <c r="B8" s="29"/>
+      <c r="C8" s="31" t="s">
         <v>84</v>
       </c>
-      <c r="D8" s="30"/>
-      <c r="E8" s="30"/>
-      <c r="F8" s="30"/>
-      <c r="G8" s="22"/>
+      <c r="D8" s="28"/>
+      <c r="E8" s="28"/>
+      <c r="F8" s="28"/>
+      <c r="G8" s="29"/>
     </row>
     <row r="9" spans="1:7" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="27" t="s">
+      <c r="A9" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="22"/>
-      <c r="C9" s="35" t="s">
+      <c r="B9" s="29"/>
+      <c r="C9" s="31" t="s">
         <v>86</v>
       </c>
-      <c r="D9" s="30"/>
-      <c r="E9" s="30"/>
-      <c r="F9" s="30"/>
-      <c r="G9" s="22"/>
+      <c r="D9" s="28"/>
+      <c r="E9" s="28"/>
+      <c r="F9" s="28"/>
+      <c r="G9" s="29"/>
     </row>
     <row r="10" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A10" s="41" t="s">
+      <c r="A10" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="B10" s="42"/>
+      <c r="B10" s="47"/>
       <c r="C10" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D10" s="66" t="s">
+      <c r="D10" s="69" t="s">
         <v>18</v>
       </c>
-      <c r="E10" s="67"/>
-      <c r="F10" s="66" t="s">
+      <c r="E10" s="70"/>
+      <c r="F10" s="69" t="s">
         <v>18</v>
       </c>
-      <c r="G10" s="67"/>
+      <c r="G10" s="70"/>
     </row>
     <row r="11" spans="1:7" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="43"/>
-      <c r="B11" s="44"/>
-      <c r="C11" s="71">
+      <c r="A11" s="48"/>
+      <c r="B11" s="49"/>
+      <c r="C11" s="21">
         <v>1</v>
       </c>
-      <c r="D11" s="69" t="s">
+      <c r="D11" s="67" t="s">
         <v>88</v>
       </c>
-      <c r="E11" s="69"/>
-      <c r="F11" s="68"/>
-      <c r="G11" s="68"/>
+      <c r="E11" s="67"/>
+      <c r="F11" s="71"/>
+      <c r="G11" s="71"/>
     </row>
     <row r="12" spans="1:7" ht="43.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="43"/>
-      <c r="B12" s="44"/>
-      <c r="C12" s="71">
+      <c r="A12" s="48"/>
+      <c r="B12" s="49"/>
+      <c r="C12" s="21">
         <v>2</v>
       </c>
-      <c r="D12" s="69" t="s">
+      <c r="D12" s="67" t="s">
         <v>89</v>
       </c>
-      <c r="E12" s="69"/>
-      <c r="F12" s="69" t="s">
+      <c r="E12" s="67"/>
+      <c r="F12" s="67" t="s">
         <v>196</v>
       </c>
-      <c r="G12" s="69"/>
+      <c r="G12" s="67"/>
     </row>
     <row r="13" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="43"/>
-      <c r="B13" s="44"/>
-      <c r="C13" s="71">
+      <c r="A13" s="48"/>
+      <c r="B13" s="49"/>
+      <c r="C13" s="21">
         <v>3</v>
       </c>
-      <c r="D13" s="69"/>
-      <c r="E13" s="69"/>
-      <c r="F13" s="69" t="s">
+      <c r="D13" s="67"/>
+      <c r="E13" s="67"/>
+      <c r="F13" s="67" t="s">
         <v>197</v>
       </c>
-      <c r="G13" s="69"/>
+      <c r="G13" s="67"/>
     </row>
     <row r="14" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="43"/>
-      <c r="B14" s="44"/>
-      <c r="C14" s="71">
+      <c r="A14" s="48"/>
+      <c r="B14" s="49"/>
+      <c r="C14" s="21">
         <v>4</v>
       </c>
-      <c r="D14" s="69" t="s">
+      <c r="D14" s="67" t="s">
         <v>90</v>
       </c>
-      <c r="E14" s="69"/>
-      <c r="F14" s="69" t="s">
+      <c r="E14" s="67"/>
+      <c r="F14" s="67" t="s">
         <v>198</v>
       </c>
-      <c r="G14" s="69"/>
+      <c r="G14" s="67"/>
     </row>
     <row r="15" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="43"/>
-      <c r="B15" s="44"/>
-      <c r="C15" s="71">
+      <c r="A15" s="48"/>
+      <c r="B15" s="49"/>
+      <c r="C15" s="21">
         <v>5</v>
       </c>
-      <c r="D15" s="69" t="s">
+      <c r="D15" s="67" t="s">
         <v>91</v>
       </c>
-      <c r="E15" s="69"/>
-      <c r="F15" s="69" t="s">
+      <c r="E15" s="67"/>
+      <c r="F15" s="67" t="s">
         <v>199</v>
       </c>
-      <c r="G15" s="69"/>
+      <c r="G15" s="67"/>
     </row>
     <row r="16" spans="1:7" ht="47.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="43"/>
-      <c r="B16" s="44"/>
-      <c r="C16" s="71">
+      <c r="A16" s="48"/>
+      <c r="B16" s="49"/>
+      <c r="C16" s="21">
         <v>6</v>
       </c>
-      <c r="D16" s="69" t="s">
+      <c r="D16" s="67" t="s">
         <v>94</v>
       </c>
-      <c r="E16" s="69"/>
-      <c r="F16" s="70"/>
-      <c r="G16" s="70"/>
+      <c r="E16" s="67"/>
+      <c r="F16" s="68"/>
+      <c r="G16" s="68"/>
     </row>
     <row r="17" spans="1:7" ht="56.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="43"/>
-      <c r="B17" s="44"/>
-      <c r="C17" s="71">
+      <c r="A17" s="48"/>
+      <c r="B17" s="49"/>
+      <c r="C17" s="21">
         <v>7</v>
       </c>
-      <c r="D17" s="69" t="s">
+      <c r="D17" s="67" t="s">
         <v>200</v>
       </c>
-      <c r="E17" s="69"/>
-      <c r="F17" s="70"/>
-      <c r="G17" s="70"/>
+      <c r="E17" s="67"/>
+      <c r="F17" s="68"/>
+      <c r="G17" s="68"/>
     </row>
     <row r="18" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="23" t="s">
+      <c r="A18" s="35" t="s">
         <v>19</v>
       </c>
-      <c r="B18" s="24"/>
+      <c r="B18" s="36"/>
       <c r="C18" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D18" s="72" t="s">
         <v>18</v>
       </c>
-      <c r="E18" s="34"/>
-      <c r="F18" s="34"/>
-      <c r="G18" s="26"/>
+      <c r="E18" s="44"/>
+      <c r="F18" s="44"/>
+      <c r="G18" s="40"/>
     </row>
     <row r="19" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="28"/>
-      <c r="B19" s="29"/>
+      <c r="A19" s="37"/>
+      <c r="B19" s="38"/>
       <c r="C19" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="D19" s="35" t="s">
+      <c r="D19" s="31" t="s">
         <v>92</v>
       </c>
-      <c r="E19" s="30"/>
-      <c r="F19" s="30"/>
-      <c r="G19" s="22"/>
+      <c r="E19" s="28"/>
+      <c r="F19" s="28"/>
+      <c r="G19" s="29"/>
     </row>
     <row r="20" spans="1:7" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="28"/>
-      <c r="B20" s="29"/>
+      <c r="A20" s="37"/>
+      <c r="B20" s="38"/>
       <c r="C20" s="16" t="s">
         <v>74</v>
       </c>
-      <c r="D20" s="35" t="s">
+      <c r="D20" s="31" t="s">
         <v>93</v>
       </c>
-      <c r="E20" s="30"/>
-      <c r="F20" s="30"/>
-      <c r="G20" s="22"/>
+      <c r="E20" s="28"/>
+      <c r="F20" s="28"/>
+      <c r="G20" s="29"/>
     </row>
     <row r="21" spans="1:7" ht="44.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="27" t="s">
+      <c r="A21" s="41" t="s">
         <v>26</v>
       </c>
-      <c r="B21" s="22"/>
-      <c r="C21" s="35" t="s">
+      <c r="B21" s="29"/>
+      <c r="C21" s="31" t="s">
         <v>87</v>
       </c>
-      <c r="D21" s="30"/>
-      <c r="E21" s="30"/>
-      <c r="F21" s="30"/>
-      <c r="G21" s="22"/>
+      <c r="D21" s="28"/>
+      <c r="E21" s="28"/>
+      <c r="F21" s="28"/>
+      <c r="G21" s="29"/>
     </row>
     <row r="22" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="23" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -14894,32 +14894,6 @@
     <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="40">
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="C4:G4"/>
-    <mergeCell ref="C5:G5"/>
-    <mergeCell ref="D6:G6"/>
-    <mergeCell ref="D7:G7"/>
-    <mergeCell ref="C8:G8"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:G1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:E2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A6:B7"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="A9:B9"/>
     <mergeCell ref="A10:B17"/>
     <mergeCell ref="A18:B20"/>
     <mergeCell ref="D19:G19"/>
@@ -14934,6 +14908,32 @@
     <mergeCell ref="D14:E14"/>
     <mergeCell ref="F14:G14"/>
     <mergeCell ref="D15:E15"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A6:B7"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:G1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:E2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C4:G4"/>
+    <mergeCell ref="C5:G5"/>
+    <mergeCell ref="D6:G6"/>
+    <mergeCell ref="D7:G7"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="F17:G17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -14953,28 +14953,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="21" t="s">
+      <c r="B1" s="29"/>
+      <c r="C1" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="22"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="29"/>
     </row>
     <row r="2" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="22"/>
-      <c r="C2" s="38" t="s">
+      <c r="B2" s="29"/>
+      <c r="C2" s="56" t="s">
         <v>95</v>
       </c>
-      <c r="D2" s="30"/>
-      <c r="E2" s="22"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="29"/>
       <c r="F2" s="1" t="s">
         <v>4</v>
       </c>
@@ -14983,233 +14983,233 @@
       </c>
     </row>
     <row r="3" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A3" s="21" t="s">
+      <c r="A3" s="32" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="22"/>
-      <c r="C3" s="31" t="s">
+      <c r="B3" s="29"/>
+      <c r="C3" s="27" t="s">
         <v>28</v>
       </c>
-      <c r="D3" s="30"/>
-      <c r="E3" s="30"/>
-      <c r="F3" s="30"/>
-      <c r="G3" s="22"/>
+      <c r="D3" s="28"/>
+      <c r="E3" s="28"/>
+      <c r="F3" s="28"/>
+      <c r="G3" s="29"/>
     </row>
     <row r="4" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A4" s="21" t="s">
+      <c r="A4" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="22"/>
-      <c r="C4" s="32">
+      <c r="B4" s="29"/>
+      <c r="C4" s="42">
         <v>45789</v>
       </c>
-      <c r="D4" s="30"/>
-      <c r="E4" s="30"/>
-      <c r="F4" s="30"/>
-      <c r="G4" s="22"/>
+      <c r="D4" s="28"/>
+      <c r="E4" s="28"/>
+      <c r="F4" s="28"/>
+      <c r="G4" s="29"/>
     </row>
     <row r="5" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A5" s="21" t="s">
+      <c r="A5" s="32" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="22"/>
-      <c r="C5" s="31" t="s">
+      <c r="B5" s="29"/>
+      <c r="C5" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="D5" s="30"/>
-      <c r="E5" s="30"/>
-      <c r="F5" s="30"/>
-      <c r="G5" s="22"/>
+      <c r="D5" s="28"/>
+      <c r="E5" s="28"/>
+      <c r="F5" s="28"/>
+      <c r="G5" s="29"/>
     </row>
     <row r="6" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A6" s="23" t="s">
+      <c r="A6" s="35" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="24"/>
+      <c r="B6" s="36"/>
       <c r="C6" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D6" s="38" t="s">
+      <c r="D6" s="56" t="s">
         <v>77</v>
       </c>
-      <c r="E6" s="30"/>
-      <c r="F6" s="30"/>
-      <c r="G6" s="22"/>
+      <c r="E6" s="28"/>
+      <c r="F6" s="28"/>
+      <c r="G6" s="29"/>
     </row>
     <row r="7" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A7" s="25"/>
-      <c r="B7" s="26"/>
+      <c r="A7" s="39"/>
+      <c r="B7" s="40"/>
       <c r="C7" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D7" s="31"/>
-      <c r="E7" s="30"/>
-      <c r="F7" s="30"/>
-      <c r="G7" s="22"/>
+      <c r="D7" s="27"/>
+      <c r="E7" s="28"/>
+      <c r="F7" s="28"/>
+      <c r="G7" s="29"/>
     </row>
     <row r="8" spans="1:7" ht="31.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="27" t="s">
+      <c r="A8" s="41" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="22"/>
-      <c r="C8" s="35" t="s">
+      <c r="B8" s="29"/>
+      <c r="C8" s="31" t="s">
         <v>96</v>
       </c>
-      <c r="D8" s="30"/>
-      <c r="E8" s="30"/>
-      <c r="F8" s="30"/>
-      <c r="G8" s="22"/>
+      <c r="D8" s="28"/>
+      <c r="E8" s="28"/>
+      <c r="F8" s="28"/>
+      <c r="G8" s="29"/>
     </row>
     <row r="9" spans="1:7" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="27" t="s">
+      <c r="A9" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="22"/>
-      <c r="C9" s="35" t="s">
+      <c r="B9" s="29"/>
+      <c r="C9" s="31" t="s">
         <v>85</v>
       </c>
-      <c r="D9" s="30"/>
-      <c r="E9" s="30"/>
-      <c r="F9" s="30"/>
-      <c r="G9" s="22"/>
+      <c r="D9" s="28"/>
+      <c r="E9" s="28"/>
+      <c r="F9" s="28"/>
+      <c r="G9" s="29"/>
     </row>
     <row r="10" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A10" s="41" t="s">
+      <c r="A10" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="B10" s="42"/>
+      <c r="B10" s="47"/>
       <c r="C10" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D10" s="56" t="s">
+      <c r="D10" s="50" t="s">
         <v>18</v>
       </c>
-      <c r="E10" s="65"/>
-      <c r="F10" s="66" t="s">
+      <c r="E10" s="62"/>
+      <c r="F10" s="69" t="s">
         <v>18</v>
       </c>
-      <c r="G10" s="67"/>
+      <c r="G10" s="70"/>
     </row>
     <row r="11" spans="1:7" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="43"/>
-      <c r="B11" s="44"/>
+      <c r="A11" s="48"/>
+      <c r="B11" s="49"/>
       <c r="C11" s="13">
         <v>1</v>
       </c>
-      <c r="D11" s="58" t="s">
+      <c r="D11" s="53" t="s">
         <v>201</v>
       </c>
-      <c r="E11" s="59"/>
+      <c r="E11" s="54"/>
       <c r="F11" s="73"/>
       <c r="G11" s="73"/>
     </row>
     <row r="12" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="43"/>
-      <c r="B12" s="44"/>
+      <c r="A12" s="48"/>
+      <c r="B12" s="49"/>
       <c r="C12" s="13">
         <v>2</v>
       </c>
-      <c r="D12" s="58" t="s">
+      <c r="D12" s="53" t="s">
         <v>202</v>
       </c>
-      <c r="E12" s="59"/>
+      <c r="E12" s="54"/>
       <c r="F12" s="73"/>
       <c r="G12" s="73"/>
     </row>
     <row r="13" spans="1:7" ht="64.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="43"/>
-      <c r="B13" s="44"/>
+      <c r="A13" s="48"/>
+      <c r="B13" s="49"/>
       <c r="C13" s="13">
         <v>3</v>
       </c>
-      <c r="D13" s="58" t="s">
+      <c r="D13" s="53" t="s">
         <v>203</v>
       </c>
-      <c r="E13" s="59"/>
+      <c r="E13" s="54"/>
       <c r="F13" s="73" t="s">
         <v>204</v>
       </c>
       <c r="G13" s="73"/>
     </row>
     <row r="14" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="43"/>
-      <c r="B14" s="44"/>
+      <c r="A14" s="48"/>
+      <c r="B14" s="49"/>
       <c r="C14" s="13">
         <v>4</v>
       </c>
-      <c r="D14" s="58"/>
-      <c r="E14" s="59"/>
+      <c r="D14" s="53"/>
+      <c r="E14" s="54"/>
       <c r="F14" s="73" t="s">
         <v>205</v>
       </c>
       <c r="G14" s="73"/>
     </row>
     <row r="15" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="43"/>
-      <c r="B15" s="44"/>
+      <c r="A15" s="48"/>
+      <c r="B15" s="49"/>
       <c r="C15" s="13">
         <v>5</v>
       </c>
-      <c r="D15" s="58"/>
-      <c r="E15" s="59"/>
+      <c r="D15" s="53"/>
+      <c r="E15" s="54"/>
       <c r="F15" s="73" t="s">
         <v>206</v>
       </c>
       <c r="G15" s="73"/>
     </row>
     <row r="16" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="43"/>
-      <c r="B16" s="44"/>
+      <c r="A16" s="48"/>
+      <c r="B16" s="49"/>
       <c r="C16" s="13">
         <v>6</v>
       </c>
-      <c r="D16" s="58" t="s">
+      <c r="D16" s="53" t="s">
         <v>207</v>
       </c>
-      <c r="E16" s="59"/>
+      <c r="E16" s="54"/>
       <c r="F16" s="73"/>
       <c r="G16" s="73"/>
     </row>
     <row r="17" spans="1:7" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="23" t="s">
+      <c r="A17" s="35" t="s">
         <v>19</v>
       </c>
-      <c r="B17" s="24"/>
+      <c r="B17" s="36"/>
       <c r="C17" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D17" s="21" t="s">
+      <c r="D17" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="E17" s="30"/>
-      <c r="F17" s="34"/>
-      <c r="G17" s="26"/>
+      <c r="E17" s="28"/>
+      <c r="F17" s="44"/>
+      <c r="G17" s="40"/>
     </row>
     <row r="18" spans="1:7" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="28"/>
-      <c r="B18" s="29"/>
+      <c r="A18" s="37"/>
+      <c r="B18" s="38"/>
       <c r="C18" s="16" t="s">
         <v>99</v>
       </c>
-      <c r="D18" s="35" t="s">
+      <c r="D18" s="31" t="s">
         <v>98</v>
       </c>
-      <c r="E18" s="30"/>
-      <c r="F18" s="30"/>
-      <c r="G18" s="22"/>
+      <c r="E18" s="28"/>
+      <c r="F18" s="28"/>
+      <c r="G18" s="29"/>
     </row>
     <row r="19" spans="1:7" ht="47.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="27" t="s">
+      <c r="A19" s="41" t="s">
         <v>26</v>
       </c>
-      <c r="B19" s="22"/>
-      <c r="C19" s="35" t="s">
+      <c r="B19" s="29"/>
+      <c r="C19" s="31" t="s">
         <v>97</v>
       </c>
-      <c r="D19" s="30"/>
-      <c r="E19" s="30"/>
-      <c r="F19" s="30"/>
-      <c r="G19" s="22"/>
+      <c r="D19" s="28"/>
+      <c r="E19" s="28"/>
+      <c r="F19" s="28"/>
+      <c r="G19" s="29"/>
     </row>
     <row r="21" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="22" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -15908,27 +15908,6 @@
     <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="37">
-    <mergeCell ref="A10:B16"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C19:G19"/>
-    <mergeCell ref="C5:G5"/>
-    <mergeCell ref="D6:G6"/>
-    <mergeCell ref="D7:G7"/>
-    <mergeCell ref="C8:G8"/>
-    <mergeCell ref="C9:G9"/>
     <mergeCell ref="A17:B18"/>
     <mergeCell ref="A19:B19"/>
     <mergeCell ref="A1:B1"/>
@@ -15945,6 +15924,27 @@
     <mergeCell ref="A6:B7"/>
     <mergeCell ref="A8:B8"/>
     <mergeCell ref="A9:B9"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="C5:G5"/>
+    <mergeCell ref="D6:G6"/>
+    <mergeCell ref="D7:G7"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="A10:B16"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="F15:G15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait"/>
